--- a/output/version3/test/15-10/MARL/CTDE/RL-RL with CL/(RL+RL) test results.xlsx
+++ b/output/version3/test/15-10/MARL/CTDE/RL-RL with CL/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>635</v>
+        <v>669</v>
       </c>
       <c r="C2" t="n">
-        <v>573</v>
+        <v>605</v>
       </c>
       <c r="D2" t="n">
-        <v>706</v>
+        <v>621</v>
       </c>
       <c r="E2" t="n">
-        <v>645</v>
+        <v>523</v>
       </c>
       <c r="F2" t="n">
-        <v>827</v>
+        <v>632</v>
       </c>
       <c r="G2" t="n">
-        <v>713</v>
+        <v>719</v>
       </c>
       <c r="H2" t="n">
-        <v>647</v>
+        <v>630</v>
       </c>
       <c r="I2" t="n">
-        <v>716</v>
+        <v>760</v>
       </c>
       <c r="J2" t="n">
-        <v>644</v>
+        <v>681</v>
       </c>
       <c r="K2" t="n">
-        <v>730</v>
+        <v>683</v>
       </c>
       <c r="L2" t="n">
-        <v>683.6</v>
+        <v>652.3</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>671</v>
+        <v>571</v>
       </c>
       <c r="C3" t="n">
-        <v>684</v>
+        <v>657</v>
       </c>
       <c r="D3" t="n">
-        <v>703</v>
+        <v>794</v>
       </c>
       <c r="E3" t="n">
-        <v>689</v>
+        <v>781</v>
       </c>
       <c r="F3" t="n">
-        <v>677</v>
+        <v>709</v>
       </c>
       <c r="G3" t="n">
-        <v>780</v>
+        <v>679</v>
       </c>
       <c r="H3" t="n">
-        <v>660</v>
+        <v>825</v>
       </c>
       <c r="I3" t="n">
-        <v>682</v>
+        <v>592</v>
       </c>
       <c r="J3" t="n">
-        <v>817</v>
+        <v>621</v>
       </c>
       <c r="K3" t="n">
-        <v>771</v>
+        <v>730</v>
       </c>
       <c r="L3" t="n">
-        <v>713.4</v>
+        <v>695.9</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>601</v>
+        <v>733</v>
       </c>
       <c r="C4" t="n">
-        <v>665</v>
+        <v>643</v>
       </c>
       <c r="D4" t="n">
-        <v>684</v>
+        <v>727</v>
       </c>
       <c r="E4" t="n">
-        <v>655</v>
+        <v>780</v>
       </c>
       <c r="F4" t="n">
-        <v>761</v>
+        <v>648</v>
       </c>
       <c r="G4" t="n">
-        <v>729</v>
+        <v>629</v>
       </c>
       <c r="H4" t="n">
-        <v>668</v>
+        <v>609</v>
       </c>
       <c r="I4" t="n">
-        <v>873</v>
+        <v>825</v>
       </c>
       <c r="J4" t="n">
-        <v>777</v>
+        <v>638</v>
       </c>
       <c r="K4" t="n">
-        <v>664</v>
+        <v>717</v>
       </c>
       <c r="L4" t="n">
-        <v>707.7</v>
+        <v>694.9</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>584</v>
+        <v>695</v>
       </c>
       <c r="C5" t="n">
-        <v>712</v>
+        <v>641</v>
       </c>
       <c r="D5" t="n">
-        <v>726</v>
+        <v>696</v>
       </c>
       <c r="E5" t="n">
-        <v>825</v>
+        <v>799</v>
       </c>
       <c r="F5" t="n">
-        <v>550</v>
+        <v>664</v>
       </c>
       <c r="G5" t="n">
-        <v>741</v>
+        <v>754</v>
       </c>
       <c r="H5" t="n">
-        <v>671</v>
+        <v>691</v>
       </c>
       <c r="I5" t="n">
-        <v>620</v>
+        <v>604</v>
       </c>
       <c r="J5" t="n">
-        <v>617</v>
+        <v>663</v>
       </c>
       <c r="K5" t="n">
-        <v>681</v>
+        <v>761</v>
       </c>
       <c r="L5" t="n">
-        <v>672.7</v>
+        <v>696.8</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>812</v>
+        <v>630</v>
       </c>
       <c r="C6" t="n">
-        <v>719</v>
+        <v>586</v>
       </c>
       <c r="D6" t="n">
-        <v>775</v>
+        <v>681</v>
       </c>
       <c r="E6" t="n">
-        <v>863</v>
+        <v>692</v>
       </c>
       <c r="F6" t="n">
-        <v>719</v>
+        <v>684</v>
       </c>
       <c r="G6" t="n">
-        <v>737</v>
+        <v>602</v>
       </c>
       <c r="H6" t="n">
-        <v>773</v>
+        <v>738</v>
       </c>
       <c r="I6" t="n">
-        <v>677</v>
+        <v>711</v>
       </c>
       <c r="J6" t="n">
-        <v>788</v>
+        <v>663</v>
       </c>
       <c r="K6" t="n">
-        <v>747</v>
+        <v>638</v>
       </c>
       <c r="L6" t="n">
-        <v>761</v>
+        <v>662.5</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>552</v>
+        <v>790</v>
       </c>
       <c r="C7" t="n">
-        <v>586</v>
+        <v>673</v>
       </c>
       <c r="D7" t="n">
-        <v>600</v>
+        <v>566</v>
       </c>
       <c r="E7" t="n">
-        <v>538</v>
+        <v>610</v>
       </c>
       <c r="F7" t="n">
-        <v>640</v>
+        <v>656</v>
       </c>
       <c r="G7" t="n">
-        <v>565</v>
+        <v>791</v>
       </c>
       <c r="H7" t="n">
-        <v>682</v>
+        <v>610</v>
       </c>
       <c r="I7" t="n">
-        <v>610</v>
+        <v>638</v>
       </c>
       <c r="J7" t="n">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="K7" t="n">
-        <v>550</v>
+        <v>578</v>
       </c>
       <c r="L7" t="n">
-        <v>598.8</v>
+        <v>657.4</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>736</v>
+        <v>673</v>
       </c>
       <c r="C8" t="n">
-        <v>673</v>
+        <v>643</v>
       </c>
       <c r="D8" t="n">
-        <v>689</v>
+        <v>603</v>
       </c>
       <c r="E8" t="n">
-        <v>737</v>
+        <v>619</v>
       </c>
       <c r="F8" t="n">
-        <v>689</v>
+        <v>762</v>
       </c>
       <c r="G8" t="n">
-        <v>778</v>
+        <v>705</v>
       </c>
       <c r="H8" t="n">
-        <v>774</v>
+        <v>604</v>
       </c>
       <c r="I8" t="n">
-        <v>662</v>
+        <v>645</v>
       </c>
       <c r="J8" t="n">
-        <v>673</v>
+        <v>688</v>
       </c>
       <c r="K8" t="n">
-        <v>723</v>
+        <v>654</v>
       </c>
       <c r="L8" t="n">
-        <v>713.4</v>
+        <v>659.6</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>612</v>
+        <v>655</v>
       </c>
       <c r="C9" t="n">
-        <v>542</v>
+        <v>707</v>
       </c>
       <c r="D9" t="n">
-        <v>596</v>
+        <v>615</v>
       </c>
       <c r="E9" t="n">
-        <v>620</v>
+        <v>782</v>
       </c>
       <c r="F9" t="n">
-        <v>871</v>
+        <v>681</v>
       </c>
       <c r="G9" t="n">
-        <v>751</v>
+        <v>674</v>
       </c>
       <c r="H9" t="n">
-        <v>712</v>
+        <v>631</v>
       </c>
       <c r="I9" t="n">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="J9" t="n">
-        <v>679</v>
+        <v>609</v>
       </c>
       <c r="K9" t="n">
-        <v>594</v>
+        <v>618</v>
       </c>
       <c r="L9" t="n">
-        <v>668.6</v>
+        <v>667.8</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>851</v>
+        <v>782</v>
       </c>
       <c r="C10" t="n">
-        <v>774</v>
+        <v>738</v>
       </c>
       <c r="D10" t="n">
-        <v>715</v>
+        <v>811</v>
       </c>
       <c r="E10" t="n">
-        <v>777</v>
+        <v>814</v>
       </c>
       <c r="F10" t="n">
-        <v>924</v>
+        <v>764</v>
       </c>
       <c r="G10" t="n">
-        <v>814</v>
+        <v>713</v>
       </c>
       <c r="H10" t="n">
-        <v>732</v>
+        <v>650</v>
       </c>
       <c r="I10" t="n">
-        <v>724</v>
+        <v>696</v>
       </c>
       <c r="J10" t="n">
-        <v>931</v>
+        <v>710</v>
       </c>
       <c r="K10" t="n">
-        <v>774</v>
+        <v>842</v>
       </c>
       <c r="L10" t="n">
-        <v>801.6</v>
+        <v>752</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>699</v>
+        <v>641</v>
       </c>
       <c r="C11" t="n">
-        <v>726</v>
+        <v>696</v>
       </c>
       <c r="D11" t="n">
-        <v>769</v>
+        <v>698</v>
       </c>
       <c r="E11" t="n">
-        <v>783</v>
+        <v>731</v>
       </c>
       <c r="F11" t="n">
-        <v>774</v>
+        <v>666</v>
       </c>
       <c r="G11" t="n">
-        <v>793</v>
+        <v>679</v>
       </c>
       <c r="H11" t="n">
-        <v>682</v>
+        <v>615</v>
       </c>
       <c r="I11" t="n">
-        <v>873</v>
+        <v>582</v>
       </c>
       <c r="J11" t="n">
-        <v>854</v>
+        <v>589</v>
       </c>
       <c r="K11" t="n">
-        <v>745</v>
+        <v>668</v>
       </c>
       <c r="L11" t="n">
-        <v>769.8</v>
+        <v>656.5</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>905</v>
+        <v>722</v>
       </c>
       <c r="C12" t="n">
-        <v>810</v>
+        <v>632</v>
       </c>
       <c r="D12" t="n">
-        <v>740</v>
+        <v>579</v>
       </c>
       <c r="E12" t="n">
-        <v>753</v>
+        <v>617</v>
       </c>
       <c r="F12" t="n">
-        <v>712</v>
+        <v>690</v>
       </c>
       <c r="G12" t="n">
-        <v>655</v>
+        <v>618</v>
       </c>
       <c r="H12" t="n">
-        <v>871</v>
+        <v>669</v>
       </c>
       <c r="I12" t="n">
-        <v>664</v>
+        <v>845</v>
       </c>
       <c r="J12" t="n">
-        <v>685</v>
+        <v>738</v>
       </c>
       <c r="K12" t="n">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="L12" t="n">
-        <v>742.7</v>
+        <v>673.8</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>779</v>
+        <v>730</v>
       </c>
       <c r="C13" t="n">
-        <v>734</v>
+        <v>814</v>
       </c>
       <c r="D13" t="n">
-        <v>745</v>
+        <v>882</v>
       </c>
       <c r="E13" t="n">
-        <v>753</v>
+        <v>810</v>
       </c>
       <c r="F13" t="n">
-        <v>904</v>
+        <v>786</v>
       </c>
       <c r="G13" t="n">
-        <v>905</v>
+        <v>796</v>
       </c>
       <c r="H13" t="n">
-        <v>799</v>
+        <v>844</v>
       </c>
       <c r="I13" t="n">
-        <v>833</v>
+        <v>777</v>
       </c>
       <c r="J13" t="n">
-        <v>862</v>
+        <v>808</v>
       </c>
       <c r="K13" t="n">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="L13" t="n">
-        <v>816.9</v>
+        <v>809.8</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>881</v>
+        <v>819</v>
       </c>
       <c r="C14" t="n">
-        <v>696</v>
+        <v>657</v>
       </c>
       <c r="D14" t="n">
-        <v>699</v>
+        <v>714</v>
       </c>
       <c r="E14" t="n">
-        <v>905</v>
+        <v>736</v>
       </c>
       <c r="F14" t="n">
-        <v>747</v>
+        <v>758</v>
       </c>
       <c r="G14" t="n">
-        <v>782</v>
+        <v>737</v>
       </c>
       <c r="H14" t="n">
-        <v>775</v>
+        <v>751</v>
       </c>
       <c r="I14" t="n">
-        <v>713</v>
+        <v>728</v>
       </c>
       <c r="J14" t="n">
-        <v>834</v>
+        <v>756</v>
       </c>
       <c r="K14" t="n">
-        <v>943</v>
+        <v>817</v>
       </c>
       <c r="L14" t="n">
-        <v>797.5</v>
+        <v>747.3</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>850</v>
+        <v>690</v>
       </c>
       <c r="C15" t="n">
-        <v>809</v>
+        <v>617</v>
       </c>
       <c r="D15" t="n">
-        <v>805</v>
+        <v>641</v>
       </c>
       <c r="E15" t="n">
-        <v>862</v>
+        <v>767</v>
       </c>
       <c r="F15" t="n">
-        <v>851</v>
+        <v>722</v>
       </c>
       <c r="G15" t="n">
-        <v>857</v>
+        <v>716</v>
       </c>
       <c r="H15" t="n">
-        <v>753</v>
+        <v>687</v>
       </c>
       <c r="I15" t="n">
-        <v>648</v>
+        <v>597</v>
       </c>
       <c r="J15" t="n">
-        <v>932</v>
+        <v>692</v>
       </c>
       <c r="K15" t="n">
-        <v>746</v>
+        <v>679</v>
       </c>
       <c r="L15" t="n">
-        <v>811.3</v>
+        <v>680.8</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>817</v>
+        <v>701</v>
       </c>
       <c r="C16" t="n">
+        <v>652</v>
+      </c>
+      <c r="D16" t="n">
+        <v>722</v>
+      </c>
+      <c r="E16" t="n">
+        <v>867</v>
+      </c>
+      <c r="F16" t="n">
+        <v>700</v>
+      </c>
+      <c r="G16" t="n">
+        <v>722</v>
+      </c>
+      <c r="H16" t="n">
+        <v>688</v>
+      </c>
+      <c r="I16" t="n">
+        <v>699</v>
+      </c>
+      <c r="J16" t="n">
         <v>690</v>
       </c>
-      <c r="D16" t="n">
-        <v>744</v>
-      </c>
-      <c r="E16" t="n">
-        <v>767</v>
-      </c>
-      <c r="F16" t="n">
-        <v>725</v>
-      </c>
-      <c r="G16" t="n">
-        <v>714</v>
-      </c>
-      <c r="H16" t="n">
-        <v>852</v>
-      </c>
-      <c r="I16" t="n">
-        <v>752</v>
-      </c>
-      <c r="J16" t="n">
-        <v>691</v>
-      </c>
       <c r="K16" t="n">
-        <v>743</v>
+        <v>671</v>
       </c>
       <c r="L16" t="n">
-        <v>749.5</v>
+        <v>711.2</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>786</v>
+        <v>647</v>
       </c>
       <c r="C17" t="n">
-        <v>817</v>
+        <v>638</v>
       </c>
       <c r="D17" t="n">
-        <v>826</v>
+        <v>631</v>
       </c>
       <c r="E17" t="n">
-        <v>839</v>
+        <v>604</v>
       </c>
       <c r="F17" t="n">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="G17" t="n">
-        <v>736</v>
+        <v>660</v>
       </c>
       <c r="H17" t="n">
-        <v>786</v>
+        <v>593</v>
       </c>
       <c r="I17" t="n">
-        <v>786</v>
+        <v>657</v>
       </c>
       <c r="J17" t="n">
-        <v>702</v>
+        <v>601</v>
       </c>
       <c r="K17" t="n">
-        <v>705</v>
+        <v>611</v>
       </c>
       <c r="L17" t="n">
-        <v>767.6</v>
+        <v>633.1</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>796</v>
+        <v>763</v>
       </c>
       <c r="C18" t="n">
-        <v>788</v>
+        <v>715</v>
       </c>
       <c r="D18" t="n">
-        <v>829</v>
+        <v>695</v>
       </c>
       <c r="E18" t="n">
-        <v>791</v>
+        <v>693</v>
       </c>
       <c r="F18" t="n">
-        <v>861</v>
+        <v>697</v>
       </c>
       <c r="G18" t="n">
-        <v>788</v>
+        <v>622</v>
       </c>
       <c r="H18" t="n">
-        <v>751</v>
+        <v>765</v>
       </c>
       <c r="I18" t="n">
-        <v>726</v>
+        <v>775</v>
       </c>
       <c r="J18" t="n">
-        <v>789</v>
+        <v>670</v>
       </c>
       <c r="K18" t="n">
-        <v>747</v>
+        <v>682</v>
       </c>
       <c r="L18" t="n">
-        <v>786.6</v>
+        <v>707.7</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>764</v>
+        <v>747</v>
       </c>
       <c r="C19" t="n">
-        <v>764</v>
+        <v>811</v>
       </c>
       <c r="D19" t="n">
-        <v>821</v>
+        <v>699</v>
       </c>
       <c r="E19" t="n">
-        <v>841</v>
+        <v>817</v>
       </c>
       <c r="F19" t="n">
-        <v>824</v>
+        <v>799</v>
       </c>
       <c r="G19" t="n">
-        <v>810</v>
+        <v>863</v>
       </c>
       <c r="H19" t="n">
-        <v>676</v>
+        <v>659</v>
       </c>
       <c r="I19" t="n">
-        <v>694</v>
+        <v>649</v>
       </c>
       <c r="J19" t="n">
-        <v>761</v>
+        <v>729</v>
       </c>
       <c r="K19" t="n">
-        <v>774</v>
+        <v>822</v>
       </c>
       <c r="L19" t="n">
-        <v>772.9</v>
+        <v>759.5</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>836</v>
+        <v>859</v>
       </c>
       <c r="C20" t="n">
-        <v>767</v>
+        <v>748</v>
       </c>
       <c r="D20" t="n">
-        <v>887</v>
+        <v>811</v>
       </c>
       <c r="E20" t="n">
+        <v>726</v>
+      </c>
+      <c r="F20" t="n">
+        <v>730</v>
+      </c>
+      <c r="G20" t="n">
+        <v>884</v>
+      </c>
+      <c r="H20" t="n">
+        <v>829</v>
+      </c>
+      <c r="I20" t="n">
+        <v>689</v>
+      </c>
+      <c r="J20" t="n">
+        <v>832</v>
+      </c>
+      <c r="K20" t="n">
         <v>790</v>
       </c>
-      <c r="F20" t="n">
-        <v>789</v>
-      </c>
-      <c r="G20" t="n">
-        <v>755</v>
-      </c>
-      <c r="H20" t="n">
-        <v>904</v>
-      </c>
-      <c r="I20" t="n">
-        <v>799</v>
-      </c>
-      <c r="J20" t="n">
-        <v>908</v>
-      </c>
-      <c r="K20" t="n">
-        <v>840</v>
-      </c>
       <c r="L20" t="n">
-        <v>827.5</v>
+        <v>789.8</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>810</v>
+        <v>754</v>
       </c>
       <c r="C21" t="n">
-        <v>744</v>
+        <v>703</v>
       </c>
       <c r="D21" t="n">
-        <v>747</v>
+        <v>650</v>
       </c>
       <c r="E21" t="n">
-        <v>828</v>
+        <v>664</v>
       </c>
       <c r="F21" t="n">
-        <v>891</v>
+        <v>686</v>
       </c>
       <c r="G21" t="n">
-        <v>765</v>
+        <v>678</v>
       </c>
       <c r="H21" t="n">
-        <v>914</v>
+        <v>653</v>
       </c>
       <c r="I21" t="n">
-        <v>765</v>
+        <v>754</v>
       </c>
       <c r="J21" t="n">
-        <v>788</v>
+        <v>768</v>
       </c>
       <c r="K21" t="n">
-        <v>719</v>
+        <v>665</v>
       </c>
       <c r="L21" t="n">
-        <v>797.1</v>
+        <v>697.5</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>755</v>
+        <v>698</v>
       </c>
       <c r="C22" t="n">
-        <v>813</v>
+        <v>628</v>
       </c>
       <c r="D22" t="n">
-        <v>729</v>
+        <v>584</v>
       </c>
       <c r="E22" t="n">
-        <v>842</v>
+        <v>780</v>
       </c>
       <c r="F22" t="n">
-        <v>758</v>
+        <v>651</v>
       </c>
       <c r="G22" t="n">
-        <v>841</v>
+        <v>665</v>
       </c>
       <c r="H22" t="n">
-        <v>697</v>
+        <v>679</v>
       </c>
       <c r="I22" t="n">
-        <v>820</v>
+        <v>714</v>
       </c>
       <c r="J22" t="n">
-        <v>696</v>
+        <v>756</v>
       </c>
       <c r="K22" t="n">
-        <v>713</v>
+        <v>644</v>
       </c>
       <c r="L22" t="n">
-        <v>766.4</v>
+        <v>679.9</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="C23" t="n">
-        <v>737</v>
+        <v>722</v>
       </c>
       <c r="D23" t="n">
-        <v>749</v>
+        <v>637</v>
       </c>
       <c r="E23" t="n">
-        <v>802</v>
+        <v>697</v>
       </c>
       <c r="F23" t="n">
-        <v>773</v>
+        <v>685</v>
       </c>
       <c r="G23" t="n">
-        <v>758</v>
+        <v>674</v>
       </c>
       <c r="H23" t="n">
-        <v>734</v>
+        <v>655</v>
       </c>
       <c r="I23" t="n">
-        <v>794</v>
+        <v>634</v>
       </c>
       <c r="J23" t="n">
-        <v>883</v>
+        <v>747</v>
       </c>
       <c r="K23" t="n">
-        <v>727</v>
+        <v>629</v>
       </c>
       <c r="L23" t="n">
-        <v>767.4</v>
+        <v>680.5</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>809</v>
+        <v>665</v>
       </c>
       <c r="C24" t="n">
-        <v>760</v>
+        <v>771</v>
       </c>
       <c r="D24" t="n">
-        <v>775</v>
+        <v>717</v>
       </c>
       <c r="E24" t="n">
-        <v>753</v>
+        <v>847</v>
       </c>
       <c r="F24" t="n">
-        <v>818</v>
+        <v>637</v>
       </c>
       <c r="G24" t="n">
-        <v>802</v>
+        <v>739</v>
       </c>
       <c r="H24" t="n">
-        <v>690</v>
+        <v>653</v>
       </c>
       <c r="I24" t="n">
-        <v>715</v>
+        <v>674</v>
       </c>
       <c r="J24" t="n">
-        <v>728</v>
+        <v>741</v>
       </c>
       <c r="K24" t="n">
-        <v>828</v>
+        <v>756</v>
       </c>
       <c r="L24" t="n">
-        <v>767.8</v>
+        <v>720</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>730</v>
+        <v>666</v>
       </c>
       <c r="C25" t="n">
-        <v>725</v>
+        <v>604</v>
       </c>
       <c r="D25" t="n">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="E25" t="n">
-        <v>710</v>
+        <v>653</v>
       </c>
       <c r="F25" t="n">
-        <v>767</v>
+        <v>701</v>
       </c>
       <c r="G25" t="n">
-        <v>696</v>
+        <v>803</v>
       </c>
       <c r="H25" t="n">
-        <v>791</v>
+        <v>635</v>
       </c>
       <c r="I25" t="n">
-        <v>642</v>
+        <v>753</v>
       </c>
       <c r="J25" t="n">
-        <v>741</v>
+        <v>690</v>
       </c>
       <c r="K25" t="n">
-        <v>711</v>
+        <v>624</v>
       </c>
       <c r="L25" t="n">
-        <v>721.2</v>
+        <v>683.1</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>911</v>
+        <v>780</v>
       </c>
       <c r="C26" t="n">
-        <v>791</v>
+        <v>819</v>
       </c>
       <c r="D26" t="n">
-        <v>795</v>
+        <v>676</v>
       </c>
       <c r="E26" t="n">
-        <v>811</v>
+        <v>663</v>
       </c>
       <c r="F26" t="n">
-        <v>842</v>
+        <v>831</v>
       </c>
       <c r="G26" t="n">
-        <v>810</v>
+        <v>832</v>
       </c>
       <c r="H26" t="n">
-        <v>769</v>
+        <v>790</v>
       </c>
       <c r="I26" t="n">
-        <v>759</v>
+        <v>819</v>
       </c>
       <c r="J26" t="n">
-        <v>742</v>
+        <v>705</v>
       </c>
       <c r="K26" t="n">
-        <v>876</v>
+        <v>779</v>
       </c>
       <c r="L26" t="n">
-        <v>810.6</v>
+        <v>769.4</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>775</v>
+        <v>741</v>
       </c>
       <c r="C27" t="n">
-        <v>666</v>
+        <v>610</v>
       </c>
       <c r="D27" t="n">
-        <v>616</v>
+        <v>645</v>
       </c>
       <c r="E27" t="n">
-        <v>641</v>
+        <v>587</v>
       </c>
       <c r="F27" t="n">
-        <v>694</v>
+        <v>618</v>
       </c>
       <c r="G27" t="n">
-        <v>719</v>
+        <v>560</v>
       </c>
       <c r="H27" t="n">
-        <v>683</v>
+        <v>587</v>
       </c>
       <c r="I27" t="n">
-        <v>684</v>
+        <v>643</v>
       </c>
       <c r="J27" t="n">
-        <v>784</v>
+        <v>674</v>
       </c>
       <c r="K27" t="n">
-        <v>814</v>
+        <v>671</v>
       </c>
       <c r="L27" t="n">
-        <v>707.6</v>
+        <v>633.6</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>847</v>
+        <v>635</v>
       </c>
       <c r="C28" t="n">
-        <v>740</v>
+        <v>660</v>
       </c>
       <c r="D28" t="n">
-        <v>875</v>
+        <v>734</v>
       </c>
       <c r="E28" t="n">
-        <v>618</v>
+        <v>693</v>
       </c>
       <c r="F28" t="n">
-        <v>689</v>
+        <v>665</v>
       </c>
       <c r="G28" t="n">
+        <v>638</v>
+      </c>
+      <c r="H28" t="n">
         <v>701</v>
       </c>
-      <c r="H28" t="n">
-        <v>818</v>
-      </c>
       <c r="I28" t="n">
-        <v>736</v>
+        <v>583</v>
       </c>
       <c r="J28" t="n">
-        <v>619</v>
+        <v>669</v>
       </c>
       <c r="K28" t="n">
-        <v>716</v>
+        <v>553</v>
       </c>
       <c r="L28" t="n">
-        <v>735.9</v>
+        <v>653.1</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>695</v>
+        <v>732</v>
       </c>
       <c r="C29" t="n">
-        <v>750</v>
+        <v>765</v>
       </c>
       <c r="D29" t="n">
-        <v>705</v>
+        <v>872</v>
       </c>
       <c r="E29" t="n">
-        <v>637</v>
+        <v>690</v>
       </c>
       <c r="F29" t="n">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="G29" t="n">
-        <v>712</v>
+        <v>759</v>
       </c>
       <c r="H29" t="n">
-        <v>693</v>
+        <v>671</v>
       </c>
       <c r="I29" t="n">
-        <v>729</v>
+        <v>681</v>
       </c>
       <c r="J29" t="n">
-        <v>686</v>
+        <v>787</v>
       </c>
       <c r="K29" t="n">
-        <v>582</v>
+        <v>728</v>
       </c>
       <c r="L29" t="n">
-        <v>688.6</v>
+        <v>738.9</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>751</v>
+        <v>651</v>
       </c>
       <c r="C30" t="n">
-        <v>659</v>
+        <v>745</v>
       </c>
       <c r="D30" t="n">
-        <v>827</v>
+        <v>654</v>
       </c>
       <c r="E30" t="n">
-        <v>804</v>
+        <v>789</v>
       </c>
       <c r="F30" t="n">
-        <v>867</v>
+        <v>688</v>
       </c>
       <c r="G30" t="n">
-        <v>701</v>
+        <v>656</v>
       </c>
       <c r="H30" t="n">
-        <v>646</v>
+        <v>743</v>
       </c>
       <c r="I30" t="n">
-        <v>739</v>
+        <v>560</v>
       </c>
       <c r="J30" t="n">
-        <v>773</v>
+        <v>676</v>
       </c>
       <c r="K30" t="n">
-        <v>792</v>
+        <v>647</v>
       </c>
       <c r="L30" t="n">
-        <v>755.9</v>
+        <v>680.9</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>832</v>
+        <v>656</v>
       </c>
       <c r="C31" t="n">
-        <v>893</v>
+        <v>679</v>
       </c>
       <c r="D31" t="n">
-        <v>920</v>
+        <v>732</v>
       </c>
       <c r="E31" t="n">
-        <v>746</v>
+        <v>694</v>
       </c>
       <c r="F31" t="n">
-        <v>765</v>
+        <v>749</v>
       </c>
       <c r="G31" t="n">
-        <v>905</v>
+        <v>760</v>
       </c>
       <c r="H31" t="n">
-        <v>850</v>
+        <v>721</v>
       </c>
       <c r="I31" t="n">
-        <v>944</v>
+        <v>661</v>
       </c>
       <c r="J31" t="n">
-        <v>859</v>
+        <v>726</v>
       </c>
       <c r="K31" t="n">
-        <v>830</v>
+        <v>694</v>
       </c>
       <c r="L31" t="n">
-        <v>854.4</v>
+        <v>707.2</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>760</v>
+        <v>748</v>
       </c>
       <c r="C32" t="n">
-        <v>772</v>
+        <v>792</v>
       </c>
       <c r="D32" t="n">
-        <v>684</v>
+        <v>800</v>
       </c>
       <c r="E32" t="n">
-        <v>642</v>
+        <v>793</v>
       </c>
       <c r="F32" t="n">
-        <v>747</v>
+        <v>824</v>
       </c>
       <c r="G32" t="n">
-        <v>617</v>
+        <v>711</v>
       </c>
       <c r="H32" t="n">
-        <v>712</v>
+        <v>726</v>
       </c>
       <c r="I32" t="n">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="J32" t="n">
-        <v>624</v>
+        <v>698</v>
       </c>
       <c r="K32" t="n">
-        <v>776</v>
+        <v>784</v>
       </c>
       <c r="L32" t="n">
-        <v>708</v>
+        <v>762.4</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>716</v>
+        <v>797</v>
       </c>
       <c r="C33" t="n">
-        <v>674</v>
+        <v>761</v>
       </c>
       <c r="D33" t="n">
-        <v>842</v>
+        <v>730</v>
       </c>
       <c r="E33" t="n">
-        <v>714</v>
+        <v>576</v>
       </c>
       <c r="F33" t="n">
-        <v>814</v>
+        <v>706</v>
       </c>
       <c r="G33" t="n">
-        <v>765</v>
+        <v>925</v>
       </c>
       <c r="H33" t="n">
-        <v>772</v>
+        <v>752</v>
       </c>
       <c r="I33" t="n">
-        <v>787</v>
+        <v>677</v>
       </c>
       <c r="J33" t="n">
-        <v>929</v>
+        <v>744</v>
       </c>
       <c r="K33" t="n">
-        <v>787</v>
+        <v>838</v>
       </c>
       <c r="L33" t="n">
-        <v>780</v>
+        <v>750.6</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>799</v>
+        <v>623</v>
       </c>
       <c r="C34" t="n">
-        <v>710</v>
+        <v>812</v>
       </c>
       <c r="D34" t="n">
-        <v>754</v>
+        <v>791</v>
       </c>
       <c r="E34" t="n">
-        <v>700</v>
+        <v>753</v>
       </c>
       <c r="F34" t="n">
-        <v>663</v>
+        <v>751</v>
       </c>
       <c r="G34" t="n">
-        <v>775</v>
+        <v>720</v>
       </c>
       <c r="H34" t="n">
-        <v>668</v>
+        <v>691</v>
       </c>
       <c r="I34" t="n">
-        <v>663</v>
+        <v>779</v>
       </c>
       <c r="J34" t="n">
-        <v>829</v>
+        <v>641</v>
       </c>
       <c r="K34" t="n">
-        <v>696</v>
+        <v>766</v>
       </c>
       <c r="L34" t="n">
-        <v>725.7</v>
+        <v>732.7</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>935</v>
+        <v>763</v>
       </c>
       <c r="C35" t="n">
-        <v>602</v>
+        <v>591</v>
       </c>
       <c r="D35" t="n">
-        <v>651</v>
+        <v>720</v>
       </c>
       <c r="E35" t="n">
-        <v>687</v>
+        <v>613</v>
       </c>
       <c r="F35" t="n">
-        <v>796</v>
+        <v>739</v>
       </c>
       <c r="G35" t="n">
-        <v>614</v>
+        <v>680</v>
       </c>
       <c r="H35" t="n">
-        <v>607</v>
+        <v>575</v>
       </c>
       <c r="I35" t="n">
-        <v>702</v>
+        <v>565</v>
       </c>
       <c r="J35" t="n">
-        <v>672</v>
+        <v>647</v>
       </c>
       <c r="K35" t="n">
-        <v>652</v>
+        <v>546</v>
       </c>
       <c r="L35" t="n">
-        <v>691.8</v>
+        <v>643.9</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>822</v>
+        <v>707</v>
       </c>
       <c r="C36" t="n">
-        <v>604</v>
+        <v>687</v>
       </c>
       <c r="D36" t="n">
-        <v>726</v>
+        <v>711</v>
       </c>
       <c r="E36" t="n">
-        <v>652</v>
+        <v>747</v>
       </c>
       <c r="F36" t="n">
-        <v>702</v>
+        <v>683</v>
       </c>
       <c r="G36" t="n">
-        <v>691</v>
+        <v>792</v>
       </c>
       <c r="H36" t="n">
-        <v>809</v>
+        <v>784</v>
       </c>
       <c r="I36" t="n">
-        <v>856</v>
+        <v>796</v>
       </c>
       <c r="J36" t="n">
-        <v>809</v>
+        <v>795</v>
       </c>
       <c r="K36" t="n">
-        <v>884</v>
+        <v>655</v>
       </c>
       <c r="L36" t="n">
-        <v>755.5</v>
+        <v>735.7</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C37" t="n">
-        <v>808</v>
+        <v>746</v>
       </c>
       <c r="D37" t="n">
-        <v>776</v>
+        <v>677</v>
       </c>
       <c r="E37" t="n">
-        <v>813</v>
+        <v>705</v>
       </c>
       <c r="F37" t="n">
-        <v>803</v>
+        <v>741</v>
       </c>
       <c r="G37" t="n">
-        <v>768</v>
+        <v>724</v>
       </c>
       <c r="H37" t="n">
-        <v>682</v>
+        <v>654</v>
       </c>
       <c r="I37" t="n">
-        <v>705</v>
+        <v>650</v>
       </c>
       <c r="J37" t="n">
-        <v>726</v>
+        <v>771</v>
       </c>
       <c r="K37" t="n">
-        <v>724</v>
+        <v>669</v>
       </c>
       <c r="L37" t="n">
-        <v>753.3</v>
+        <v>706.3</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C38" t="n">
-        <v>645</v>
+        <v>728</v>
       </c>
       <c r="D38" t="n">
-        <v>911</v>
+        <v>646</v>
       </c>
       <c r="E38" t="n">
-        <v>732</v>
+        <v>788</v>
       </c>
       <c r="F38" t="n">
-        <v>795</v>
+        <v>649</v>
       </c>
       <c r="G38" t="n">
-        <v>626</v>
+        <v>650</v>
       </c>
       <c r="H38" t="n">
-        <v>676</v>
+        <v>716</v>
       </c>
       <c r="I38" t="n">
-        <v>742</v>
+        <v>717</v>
       </c>
       <c r="J38" t="n">
-        <v>703</v>
+        <v>652</v>
       </c>
       <c r="K38" t="n">
-        <v>798</v>
+        <v>810</v>
       </c>
       <c r="L38" t="n">
-        <v>726.5</v>
+        <v>699.4</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>632</v>
+        <v>590</v>
       </c>
       <c r="C39" t="n">
-        <v>600</v>
+        <v>552</v>
       </c>
       <c r="D39" t="n">
-        <v>561</v>
+        <v>633</v>
       </c>
       <c r="E39" t="n">
-        <v>593</v>
+        <v>560</v>
       </c>
       <c r="F39" t="n">
-        <v>510</v>
+        <v>675</v>
       </c>
       <c r="G39" t="n">
-        <v>673</v>
+        <v>754</v>
       </c>
       <c r="H39" t="n">
-        <v>501</v>
+        <v>567</v>
       </c>
       <c r="I39" t="n">
-        <v>586</v>
+        <v>652</v>
       </c>
       <c r="J39" t="n">
-        <v>666</v>
+        <v>774</v>
       </c>
       <c r="K39" t="n">
-        <v>699</v>
+        <v>613</v>
       </c>
       <c r="L39" t="n">
-        <v>602.1</v>
+        <v>637</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>844</v>
+        <v>898</v>
       </c>
       <c r="C40" t="n">
-        <v>693</v>
+        <v>860</v>
       </c>
       <c r="D40" t="n">
-        <v>882</v>
+        <v>673</v>
       </c>
       <c r="E40" t="n">
-        <v>657</v>
+        <v>690</v>
       </c>
       <c r="F40" t="n">
-        <v>758</v>
+        <v>622</v>
       </c>
       <c r="G40" t="n">
-        <v>648</v>
+        <v>747</v>
       </c>
       <c r="H40" t="n">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="I40" t="n">
-        <v>714</v>
+        <v>848</v>
       </c>
       <c r="J40" t="n">
-        <v>866</v>
+        <v>708</v>
       </c>
       <c r="K40" t="n">
-        <v>643</v>
+        <v>832</v>
       </c>
       <c r="L40" t="n">
-        <v>739.5</v>
+        <v>757.2</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>709</v>
+        <v>617</v>
       </c>
       <c r="C41" t="n">
-        <v>612</v>
+        <v>632</v>
       </c>
       <c r="D41" t="n">
+        <v>622</v>
+      </c>
+      <c r="E41" t="n">
         <v>685</v>
       </c>
-      <c r="E41" t="n">
-        <v>754</v>
-      </c>
       <c r="F41" t="n">
-        <v>678</v>
+        <v>785</v>
       </c>
       <c r="G41" t="n">
-        <v>701</v>
+        <v>592</v>
       </c>
       <c r="H41" t="n">
+        <v>733</v>
+      </c>
+      <c r="I41" t="n">
+        <v>647</v>
+      </c>
+      <c r="J41" t="n">
+        <v>608</v>
+      </c>
+      <c r="K41" t="n">
         <v>718</v>
       </c>
-      <c r="I41" t="n">
-        <v>663</v>
-      </c>
-      <c r="J41" t="n">
-        <v>920</v>
-      </c>
-      <c r="K41" t="n">
-        <v>810</v>
-      </c>
       <c r="L41" t="n">
-        <v>725</v>
+        <v>663.9</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>939</v>
+        <v>789</v>
       </c>
       <c r="C42" t="n">
-        <v>687</v>
+        <v>745</v>
       </c>
       <c r="D42" t="n">
-        <v>660</v>
+        <v>788</v>
       </c>
       <c r="E42" t="n">
-        <v>773</v>
+        <v>727</v>
       </c>
       <c r="F42" t="n">
-        <v>716</v>
+        <v>790</v>
       </c>
       <c r="G42" t="n">
-        <v>823</v>
+        <v>775</v>
       </c>
       <c r="H42" t="n">
-        <v>686</v>
+        <v>700</v>
       </c>
       <c r="I42" t="n">
-        <v>669</v>
+        <v>800</v>
       </c>
       <c r="J42" t="n">
-        <v>852</v>
+        <v>751</v>
       </c>
       <c r="K42" t="n">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="L42" t="n">
-        <v>759.7</v>
+        <v>765.5</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>898</v>
+        <v>767</v>
       </c>
       <c r="C43" t="n">
-        <v>827</v>
+        <v>731</v>
       </c>
       <c r="D43" t="n">
+        <v>884</v>
+      </c>
+      <c r="E43" t="n">
+        <v>716</v>
+      </c>
+      <c r="F43" t="n">
+        <v>750</v>
+      </c>
+      <c r="G43" t="n">
+        <v>857</v>
+      </c>
+      <c r="H43" t="n">
         <v>773</v>
       </c>
-      <c r="E43" t="n">
-        <v>856</v>
-      </c>
-      <c r="F43" t="n">
-        <v>794</v>
-      </c>
-      <c r="G43" t="n">
-        <v>967</v>
-      </c>
-      <c r="H43" t="n">
-        <v>741</v>
-      </c>
       <c r="I43" t="n">
-        <v>755</v>
+        <v>770</v>
       </c>
       <c r="J43" t="n">
-        <v>728</v>
+        <v>798</v>
       </c>
       <c r="K43" t="n">
-        <v>782</v>
+        <v>687</v>
       </c>
       <c r="L43" t="n">
-        <v>812.1</v>
+        <v>773.3</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>659</v>
+        <v>720</v>
       </c>
       <c r="C44" t="n">
-        <v>744</v>
+        <v>782</v>
       </c>
       <c r="D44" t="n">
-        <v>670</v>
+        <v>597</v>
       </c>
       <c r="E44" t="n">
-        <v>717</v>
+        <v>690</v>
       </c>
       <c r="F44" t="n">
-        <v>726</v>
+        <v>699</v>
       </c>
       <c r="G44" t="n">
-        <v>677</v>
+        <v>657</v>
       </c>
       <c r="H44" t="n">
-        <v>750</v>
+        <v>737</v>
       </c>
       <c r="I44" t="n">
-        <v>746</v>
+        <v>700</v>
       </c>
       <c r="J44" t="n">
-        <v>757</v>
+        <v>705</v>
       </c>
       <c r="K44" t="n">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="L44" t="n">
-        <v>710.2</v>
+        <v>694.2</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>767</v>
+        <v>745</v>
       </c>
       <c r="C45" t="n">
-        <v>839</v>
+        <v>826</v>
       </c>
       <c r="D45" t="n">
-        <v>845</v>
+        <v>733</v>
       </c>
       <c r="E45" t="n">
-        <v>744</v>
+        <v>731</v>
       </c>
       <c r="F45" t="n">
-        <v>760</v>
+        <v>782</v>
       </c>
       <c r="G45" t="n">
-        <v>855</v>
+        <v>788</v>
       </c>
       <c r="H45" t="n">
-        <v>789</v>
+        <v>776</v>
       </c>
       <c r="I45" t="n">
-        <v>827</v>
+        <v>740</v>
       </c>
       <c r="J45" t="n">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="K45" t="n">
-        <v>919</v>
+        <v>749</v>
       </c>
       <c r="L45" t="n">
-        <v>813.8</v>
+        <v>766.8</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>806</v>
+        <v>660</v>
       </c>
       <c r="C46" t="n">
-        <v>820</v>
+        <v>681</v>
       </c>
       <c r="D46" t="n">
-        <v>613</v>
+        <v>688</v>
       </c>
       <c r="E46" t="n">
-        <v>701</v>
+        <v>807</v>
       </c>
       <c r="F46" t="n">
-        <v>609</v>
+        <v>752</v>
       </c>
       <c r="G46" t="n">
-        <v>754</v>
+        <v>621</v>
       </c>
       <c r="H46" t="n">
-        <v>674</v>
+        <v>686</v>
       </c>
       <c r="I46" t="n">
-        <v>790</v>
+        <v>733</v>
       </c>
       <c r="J46" t="n">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="K46" t="n">
-        <v>823</v>
+        <v>680</v>
       </c>
       <c r="L46" t="n">
-        <v>733.2</v>
+        <v>705.7</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>624</v>
+        <v>750</v>
       </c>
       <c r="C47" t="n">
-        <v>636</v>
+        <v>774</v>
       </c>
       <c r="D47" t="n">
-        <v>543</v>
+        <v>599</v>
       </c>
       <c r="E47" t="n">
-        <v>603</v>
+        <v>655</v>
       </c>
       <c r="F47" t="n">
-        <v>532</v>
+        <v>742</v>
       </c>
       <c r="G47" t="n">
-        <v>653</v>
+        <v>592</v>
       </c>
       <c r="H47" t="n">
-        <v>746</v>
+        <v>660</v>
       </c>
       <c r="I47" t="n">
-        <v>621</v>
+        <v>718</v>
       </c>
       <c r="J47" t="n">
-        <v>761</v>
+        <v>699</v>
       </c>
       <c r="K47" t="n">
-        <v>699</v>
+        <v>717</v>
       </c>
       <c r="L47" t="n">
-        <v>641.8</v>
+        <v>690.6</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>746</v>
+        <v>854</v>
       </c>
       <c r="C48" t="n">
-        <v>817</v>
+        <v>858</v>
       </c>
       <c r="D48" t="n">
-        <v>796</v>
+        <v>713</v>
       </c>
       <c r="E48" t="n">
-        <v>809</v>
+        <v>857</v>
       </c>
       <c r="F48" t="n">
-        <v>711</v>
+        <v>826</v>
       </c>
       <c r="G48" t="n">
-        <v>730</v>
+        <v>852</v>
       </c>
       <c r="H48" t="n">
-        <v>853</v>
+        <v>874</v>
       </c>
       <c r="I48" t="n">
-        <v>771</v>
+        <v>744</v>
       </c>
       <c r="J48" t="n">
-        <v>782</v>
+        <v>923</v>
       </c>
       <c r="K48" t="n">
-        <v>834</v>
+        <v>810</v>
       </c>
       <c r="L48" t="n">
-        <v>784.9</v>
+        <v>831.1</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>810</v>
+        <v>777</v>
       </c>
       <c r="C49" t="n">
-        <v>751</v>
+        <v>788</v>
       </c>
       <c r="D49" t="n">
-        <v>772</v>
+        <v>720</v>
       </c>
       <c r="E49" t="n">
-        <v>735</v>
+        <v>694</v>
       </c>
       <c r="F49" t="n">
-        <v>747</v>
+        <v>767</v>
       </c>
       <c r="G49" t="n">
-        <v>686</v>
+        <v>712</v>
       </c>
       <c r="H49" t="n">
-        <v>827</v>
+        <v>780</v>
       </c>
       <c r="I49" t="n">
-        <v>708</v>
+        <v>724</v>
       </c>
       <c r="J49" t="n">
-        <v>671</v>
+        <v>722</v>
       </c>
       <c r="K49" t="n">
-        <v>746</v>
+        <v>807</v>
       </c>
       <c r="L49" t="n">
-        <v>745.3</v>
+        <v>749.1</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>788</v>
+        <v>668</v>
       </c>
       <c r="C50" t="n">
-        <v>874</v>
+        <v>741</v>
       </c>
       <c r="D50" t="n">
-        <v>753</v>
+        <v>718</v>
       </c>
       <c r="E50" t="n">
-        <v>874</v>
+        <v>711</v>
       </c>
       <c r="F50" t="n">
-        <v>825</v>
+        <v>739</v>
       </c>
       <c r="G50" t="n">
-        <v>797</v>
+        <v>722</v>
       </c>
       <c r="H50" t="n">
-        <v>860</v>
+        <v>784</v>
       </c>
       <c r="I50" t="n">
-        <v>656</v>
+        <v>748</v>
       </c>
       <c r="J50" t="n">
-        <v>766</v>
+        <v>655</v>
       </c>
       <c r="K50" t="n">
-        <v>834</v>
+        <v>649</v>
       </c>
       <c r="L50" t="n">
-        <v>802.7</v>
+        <v>713.5</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>781</v>
+        <v>683</v>
       </c>
       <c r="C51" t="n">
-        <v>781</v>
+        <v>698</v>
       </c>
       <c r="D51" t="n">
-        <v>720</v>
+        <v>742</v>
       </c>
       <c r="E51" t="n">
-        <v>641</v>
+        <v>736</v>
       </c>
       <c r="F51" t="n">
-        <v>731</v>
+        <v>709</v>
       </c>
       <c r="G51" t="n">
         <v>695</v>
       </c>
       <c r="H51" t="n">
-        <v>869</v>
+        <v>803</v>
       </c>
       <c r="I51" t="n">
-        <v>837</v>
+        <v>643</v>
       </c>
       <c r="J51" t="n">
-        <v>802</v>
+        <v>822</v>
       </c>
       <c r="K51" t="n">
-        <v>655</v>
+        <v>700</v>
       </c>
       <c r="L51" t="n">
-        <v>751.2</v>
+        <v>723.1</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>763.98</v>
+        <v>714.8</v>
       </c>
       <c r="C52" t="n">
-        <v>726.0599999999999</v>
+        <v>707.28</v>
       </c>
       <c r="D52" t="n">
-        <v>742.26</v>
+        <v>699.48</v>
       </c>
       <c r="E52" t="n">
-        <v>740.4400000000001</v>
+        <v>715.1799999999999</v>
       </c>
       <c r="F52" t="n">
-        <v>750.3200000000001</v>
+        <v>715.66</v>
       </c>
       <c r="G52" t="n">
-        <v>746.5599999999999</v>
+        <v>717.86</v>
       </c>
       <c r="H52" t="n">
-        <v>741.66</v>
+        <v>700.8200000000001</v>
       </c>
       <c r="I52" t="n">
-        <v>732.64</v>
+        <v>701</v>
       </c>
       <c r="J52" t="n">
-        <v>766.12</v>
+        <v>712.78</v>
       </c>
       <c r="K52" t="n">
-        <v>749.62</v>
+        <v>706.1</v>
       </c>
       <c r="L52" t="n">
-        <v>745.9659999999999</v>
+        <v>709.096</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4.743679285049438</v>
+        <v>4.623507499694824</v>
       </c>
       <c r="C2" t="n">
-        <v>4.286480188369751</v>
+        <v>4.086655855178833</v>
       </c>
       <c r="D2" t="n">
-        <v>4.753839492797852</v>
+        <v>4.323212623596191</v>
       </c>
       <c r="E2" t="n">
-        <v>4.725661516189575</v>
+        <v>3.930678844451904</v>
       </c>
       <c r="F2" t="n">
-        <v>5.529082775115967</v>
+        <v>4.569731473922729</v>
       </c>
       <c r="G2" t="n">
-        <v>4.580069303512573</v>
+        <v>4.087106704711914</v>
       </c>
       <c r="H2" t="n">
-        <v>4.366335868835449</v>
+        <v>3.966952085494995</v>
       </c>
       <c r="I2" t="n">
-        <v>4.931155443191528</v>
+        <v>4.796450614929199</v>
       </c>
       <c r="J2" t="n">
-        <v>4.4835045337677</v>
+        <v>4.893513202667236</v>
       </c>
       <c r="K2" t="n">
-        <v>5.389068365097046</v>
+        <v>4.845065116882324</v>
       </c>
       <c r="L2" t="n">
-        <v>4.778887677192688</v>
+        <v>4.412287402153015</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>4.82414436340332</v>
+        <v>4.413956642150879</v>
       </c>
       <c r="C3" t="n">
-        <v>4.997044324874878</v>
+        <v>4.419636964797974</v>
       </c>
       <c r="D3" t="n">
-        <v>5.085959911346436</v>
+        <v>4.834969758987427</v>
       </c>
       <c r="E3" t="n">
-        <v>4.731439113616943</v>
+        <v>4.559463977813721</v>
       </c>
       <c r="F3" t="n">
-        <v>4.964408874511719</v>
+        <v>4.570489645004272</v>
       </c>
       <c r="G3" t="n">
-        <v>5.240127563476562</v>
+        <v>4.856411457061768</v>
       </c>
       <c r="H3" t="n">
-        <v>4.802459478378296</v>
+        <v>5.087189912796021</v>
       </c>
       <c r="I3" t="n">
-        <v>5.095155239105225</v>
+        <v>4.115439891815186</v>
       </c>
       <c r="J3" t="n">
-        <v>5.927311420440674</v>
+        <v>4.181020021438599</v>
       </c>
       <c r="K3" t="n">
-        <v>5.193835973739624</v>
+        <v>4.869899749755859</v>
       </c>
       <c r="L3" t="n">
-        <v>5.086188626289368</v>
+        <v>4.590847802162171</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>4.426149129867554</v>
+        <v>4.536401033401489</v>
       </c>
       <c r="C4" t="n">
-        <v>4.036584138870239</v>
+        <v>3.824866533279419</v>
       </c>
       <c r="D4" t="n">
-        <v>4.158838510513306</v>
+        <v>4.439797163009644</v>
       </c>
       <c r="E4" t="n">
-        <v>4.780133962631226</v>
+        <v>4.440445899963379</v>
       </c>
       <c r="F4" t="n">
-        <v>5.160389184951782</v>
+        <v>3.761670351028442</v>
       </c>
       <c r="G4" t="n">
-        <v>4.422391176223755</v>
+        <v>3.724028587341309</v>
       </c>
       <c r="H4" t="n">
-        <v>4.310083866119385</v>
+        <v>3.69504189491272</v>
       </c>
       <c r="I4" t="n">
-        <v>6.065934896469116</v>
+        <v>4.068747282028198</v>
       </c>
       <c r="J4" t="n">
-        <v>5.304144620895386</v>
+        <v>3.61485767364502</v>
       </c>
       <c r="K4" t="n">
-        <v>4.421675682067871</v>
+        <v>4.734639167785645</v>
       </c>
       <c r="L4" t="n">
-        <v>4.708632516860962</v>
+        <v>4.084049558639526</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>4.012872934341431</v>
+        <v>4.327198266983032</v>
       </c>
       <c r="C5" t="n">
-        <v>4.510771512985229</v>
+        <v>4.073695421218872</v>
       </c>
       <c r="D5" t="n">
-        <v>4.489892721176147</v>
+        <v>4.873663187026978</v>
       </c>
       <c r="E5" t="n">
-        <v>4.766306638717651</v>
+        <v>5.025420665740967</v>
       </c>
       <c r="F5" t="n">
-        <v>3.939739465713501</v>
+        <v>4.086484432220459</v>
       </c>
       <c r="G5" t="n">
-        <v>4.895315170288086</v>
+        <v>4.006448030471802</v>
       </c>
       <c r="H5" t="n">
-        <v>4.209531784057617</v>
+        <v>4.498741388320923</v>
       </c>
       <c r="I5" t="n">
-        <v>4.307744741439819</v>
+        <v>3.913159847259521</v>
       </c>
       <c r="J5" t="n">
-        <v>3.93558406829834</v>
+        <v>3.688223361968994</v>
       </c>
       <c r="K5" t="n">
-        <v>4.255052089691162</v>
+        <v>4.452325582504272</v>
       </c>
       <c r="L5" t="n">
-        <v>4.332281112670898</v>
+        <v>4.294536018371582</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>5.377254009246826</v>
+        <v>3.863981962203979</v>
       </c>
       <c r="C6" t="n">
-        <v>4.738020181655884</v>
+        <v>3.832093000411987</v>
       </c>
       <c r="D6" t="n">
-        <v>4.709981203079224</v>
+        <v>3.979822635650635</v>
       </c>
       <c r="E6" t="n">
-        <v>5.559542179107666</v>
+        <v>4.201526403427124</v>
       </c>
       <c r="F6" t="n">
-        <v>4.518343925476074</v>
+        <v>4.013847589492798</v>
       </c>
       <c r="G6" t="n">
-        <v>4.529395341873169</v>
+        <v>3.930784702301025</v>
       </c>
       <c r="H6" t="n">
-        <v>4.716693878173828</v>
+        <v>4.738628387451172</v>
       </c>
       <c r="I6" t="n">
-        <v>4.584181308746338</v>
+        <v>4.51404857635498</v>
       </c>
       <c r="J6" t="n">
-        <v>5.084871053695679</v>
+        <v>4.433401584625244</v>
       </c>
       <c r="K6" t="n">
-        <v>4.617932796478271</v>
+        <v>4.265464305877686</v>
       </c>
       <c r="L6" t="n">
-        <v>4.843621587753296</v>
+        <v>4.177359914779663</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>4.3492751121521</v>
+        <v>5.06815767288208</v>
       </c>
       <c r="C7" t="n">
-        <v>4.13061785697937</v>
+        <v>4.011547565460205</v>
       </c>
       <c r="D7" t="n">
-        <v>4.608226537704468</v>
+        <v>3.677864551544189</v>
       </c>
       <c r="E7" t="n">
-        <v>4.020649909973145</v>
+        <v>3.786428928375244</v>
       </c>
       <c r="F7" t="n">
-        <v>4.323161602020264</v>
+        <v>3.885964870452881</v>
       </c>
       <c r="G7" t="n">
-        <v>3.98578929901123</v>
+        <v>4.664489030838013</v>
       </c>
       <c r="H7" t="n">
-        <v>4.125911712646484</v>
+        <v>3.740387678146362</v>
       </c>
       <c r="I7" t="n">
-        <v>4.257315635681152</v>
+        <v>4.192759037017822</v>
       </c>
       <c r="J7" t="n">
-        <v>4.594127416610718</v>
+        <v>3.836936712265015</v>
       </c>
       <c r="K7" t="n">
-        <v>3.84747314453125</v>
+        <v>3.813414335250854</v>
       </c>
       <c r="L7" t="n">
-        <v>4.224254822731018</v>
+        <v>4.067795038223267</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923424959182739</v>
+        <v>4.441215515136719</v>
       </c>
       <c r="C8" t="n">
-        <v>4.891674280166626</v>
+        <v>4.376299381256104</v>
       </c>
       <c r="D8" t="n">
-        <v>4.573410987854004</v>
+        <v>4.052976608276367</v>
       </c>
       <c r="E8" t="n">
-        <v>5.480886220932007</v>
+        <v>4.813010454177856</v>
       </c>
       <c r="F8" t="n">
-        <v>4.794371366500854</v>
+        <v>5.370591163635254</v>
       </c>
       <c r="G8" t="n">
-        <v>5.862388372421265</v>
+        <v>4.444234848022461</v>
       </c>
       <c r="H8" t="n">
-        <v>6.119887113571167</v>
+        <v>3.889029979705811</v>
       </c>
       <c r="I8" t="n">
-        <v>4.966845035552979</v>
+        <v>3.879616498947144</v>
       </c>
       <c r="J8" t="n">
-        <v>5.005337715148926</v>
+        <v>4.426939010620117</v>
       </c>
       <c r="K8" t="n">
-        <v>4.729888916015625</v>
+        <v>4.013657808303833</v>
       </c>
       <c r="L8" t="n">
-        <v>5.134811496734619</v>
+        <v>4.370757126808167</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>4.285876035690308</v>
+        <v>3.753040790557861</v>
       </c>
       <c r="C9" t="n">
-        <v>3.967233896255493</v>
+        <v>3.9875648021698</v>
       </c>
       <c r="D9" t="n">
-        <v>3.908234596252441</v>
+        <v>4.251457452774048</v>
       </c>
       <c r="E9" t="n">
-        <v>3.902288436889648</v>
+        <v>4.328103065490723</v>
       </c>
       <c r="F9" t="n">
-        <v>5.712798833847046</v>
+        <v>4.475259304046631</v>
       </c>
       <c r="G9" t="n">
-        <v>4.908300399780273</v>
+        <v>3.822083950042725</v>
       </c>
       <c r="H9" t="n">
-        <v>6.271742343902588</v>
+        <v>3.594650745391846</v>
       </c>
       <c r="I9" t="n">
-        <v>4.989418983459473</v>
+        <v>3.758476257324219</v>
       </c>
       <c r="J9" t="n">
-        <v>4.462338447570801</v>
+        <v>3.655417919158936</v>
       </c>
       <c r="K9" t="n">
-        <v>4.072522640228271</v>
+        <v>3.711005926132202</v>
       </c>
       <c r="L9" t="n">
-        <v>4.648075461387634</v>
+        <v>3.933706021308899</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>5.802181243896484</v>
+        <v>5.613222122192383</v>
       </c>
       <c r="C10" t="n">
-        <v>5.302006244659424</v>
+        <v>4.822372436523438</v>
       </c>
       <c r="D10" t="n">
-        <v>5.687188386917114</v>
+        <v>5.584692716598511</v>
       </c>
       <c r="E10" t="n">
-        <v>5.890245914459229</v>
+        <v>5.81804347038269</v>
       </c>
       <c r="F10" t="n">
-        <v>6.254290342330933</v>
+        <v>6.06278657913208</v>
       </c>
       <c r="G10" t="n">
-        <v>6.565763711929321</v>
+        <v>6.176482677459717</v>
       </c>
       <c r="H10" t="n">
-        <v>5.61795449256897</v>
+        <v>5.957069873809814</v>
       </c>
       <c r="I10" t="n">
-        <v>5.028183698654175</v>
+        <v>5.270904779434204</v>
       </c>
       <c r="J10" t="n">
-        <v>5.946191787719727</v>
+        <v>4.998829364776611</v>
       </c>
       <c r="K10" t="n">
-        <v>5.919234275817871</v>
+        <v>5.327341079711914</v>
       </c>
       <c r="L10" t="n">
-        <v>5.801324009895325</v>
+        <v>5.563174510002137</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>4.729530572891235</v>
+        <v>4.674858093261719</v>
       </c>
       <c r="C11" t="n">
-        <v>5.205822944641113</v>
+        <v>4.222392797470093</v>
       </c>
       <c r="D11" t="n">
-        <v>5.508269309997559</v>
+        <v>5.424447774887085</v>
       </c>
       <c r="E11" t="n">
-        <v>5.46738076210022</v>
+        <v>5.0776047706604</v>
       </c>
       <c r="F11" t="n">
-        <v>4.616170406341553</v>
+        <v>4.909655332565308</v>
       </c>
       <c r="G11" t="n">
-        <v>5.496306419372559</v>
+        <v>5.003735303878784</v>
       </c>
       <c r="H11" t="n">
-        <v>4.874396324157715</v>
+        <v>5.508202314376831</v>
       </c>
       <c r="I11" t="n">
-        <v>5.797891855239868</v>
+        <v>9.302554368972778</v>
       </c>
       <c r="J11" t="n">
-        <v>5.735988140106201</v>
+        <v>5.250185251235962</v>
       </c>
       <c r="K11" t="n">
-        <v>5.114184617996216</v>
+        <v>4.641223192214966</v>
       </c>
       <c r="L11" t="n">
-        <v>5.254594135284424</v>
+        <v>5.401485919952393</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>4.855590343475342</v>
+        <v>5.139605045318604</v>
       </c>
       <c r="C12" t="n">
-        <v>4.832109451293945</v>
+        <v>4.608335494995117</v>
       </c>
       <c r="D12" t="n">
-        <v>4.421767711639404</v>
+        <v>4.398460865020752</v>
       </c>
       <c r="E12" t="n">
-        <v>4.666507482528687</v>
+        <v>4.249420404434204</v>
       </c>
       <c r="F12" t="n">
-        <v>4.58493185043335</v>
+        <v>4.754743576049805</v>
       </c>
       <c r="G12" t="n">
-        <v>4.591917514801025</v>
+        <v>4.082278251647949</v>
       </c>
       <c r="H12" t="n">
-        <v>4.850883007049561</v>
+        <v>4.231625556945801</v>
       </c>
       <c r="I12" t="n">
-        <v>4.215803623199463</v>
+        <v>4.488710403442383</v>
       </c>
       <c r="J12" t="n">
-        <v>4.212757349014282</v>
+        <v>3.985329866409302</v>
       </c>
       <c r="K12" t="n">
-        <v>4.165219306945801</v>
+        <v>3.755261659622192</v>
       </c>
       <c r="L12" t="n">
-        <v>4.539748764038086</v>
+        <v>4.36937711238861</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>4.913337469100952</v>
+        <v>5.356262922286987</v>
       </c>
       <c r="C13" t="n">
-        <v>5.099737644195557</v>
+        <v>5.167631387710571</v>
       </c>
       <c r="D13" t="n">
-        <v>4.704907655715942</v>
+        <v>5.610778331756592</v>
       </c>
       <c r="E13" t="n">
-        <v>5.413378238677979</v>
+        <v>5.449587345123291</v>
       </c>
       <c r="F13" t="n">
-        <v>6.184767961502075</v>
+        <v>5.078155040740967</v>
       </c>
       <c r="G13" t="n">
-        <v>5.297026395797729</v>
+        <v>5.658447265625</v>
       </c>
       <c r="H13" t="n">
-        <v>5.654868125915527</v>
+        <v>5.184629201889038</v>
       </c>
       <c r="I13" t="n">
-        <v>5.077064514160156</v>
+        <v>5.373903036117554</v>
       </c>
       <c r="J13" t="n">
-        <v>5.575504302978516</v>
+        <v>6.076967239379883</v>
       </c>
       <c r="K13" t="n">
-        <v>5.525672197341919</v>
+        <v>8.467219829559326</v>
       </c>
       <c r="L13" t="n">
-        <v>5.344626450538636</v>
+        <v>5.742358160018921</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>5.148823499679565</v>
+        <v>6.265367746353149</v>
       </c>
       <c r="C14" t="n">
-        <v>4.599948167800903</v>
+        <v>7.434107303619385</v>
       </c>
       <c r="D14" t="n">
-        <v>5.076664209365845</v>
+        <v>5.312388181686401</v>
       </c>
       <c r="E14" t="n">
-        <v>5.428527593612671</v>
+        <v>6.996895790100098</v>
       </c>
       <c r="F14" t="n">
-        <v>4.534389019012451</v>
+        <v>6.151365756988525</v>
       </c>
       <c r="G14" t="n">
-        <v>4.645795106887817</v>
+        <v>5.742088317871094</v>
       </c>
       <c r="H14" t="n">
-        <v>5.32544994354248</v>
+        <v>4.776263236999512</v>
       </c>
       <c r="I14" t="n">
-        <v>4.642277240753174</v>
+        <v>4.601694583892822</v>
       </c>
       <c r="J14" t="n">
-        <v>4.635864496231079</v>
+        <v>5.58890175819397</v>
       </c>
       <c r="K14" t="n">
-        <v>5.505145788192749</v>
+        <v>4.868979215621948</v>
       </c>
       <c r="L14" t="n">
-        <v>4.954288506507874</v>
+        <v>5.77380518913269</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>4.912296772003174</v>
+        <v>5.050833463668823</v>
       </c>
       <c r="C15" t="n">
-        <v>5.296529054641724</v>
+        <v>5.194821119308472</v>
       </c>
       <c r="D15" t="n">
-        <v>5.103140830993652</v>
+        <v>4.726361274719238</v>
       </c>
       <c r="E15" t="n">
-        <v>5.746679306030273</v>
+        <v>5.504043817520142</v>
       </c>
       <c r="F15" t="n">
-        <v>5.410430908203125</v>
+        <v>5.720844268798828</v>
       </c>
       <c r="G15" t="n">
-        <v>5.024489402770996</v>
+        <v>5.042479515075684</v>
       </c>
       <c r="H15" t="n">
-        <v>5.037863254547119</v>
+        <v>4.652599334716797</v>
       </c>
       <c r="I15" t="n">
-        <v>4.456989288330078</v>
+        <v>4.873210668563843</v>
       </c>
       <c r="J15" t="n">
-        <v>5.974621772766113</v>
+        <v>5.105404138565063</v>
       </c>
       <c r="K15" t="n">
-        <v>5.425261259078979</v>
+        <v>4.857011079788208</v>
       </c>
       <c r="L15" t="n">
-        <v>5.238830184936523</v>
+        <v>5.07276086807251</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>5.202550172805786</v>
+        <v>4.902887582778931</v>
       </c>
       <c r="C16" t="n">
-        <v>4.218218326568604</v>
+        <v>5.003619194030762</v>
       </c>
       <c r="D16" t="n">
-        <v>4.368518114089966</v>
+        <v>4.411203622817993</v>
       </c>
       <c r="E16" t="n">
-        <v>4.894504070281982</v>
+        <v>4.973699569702148</v>
       </c>
       <c r="F16" t="n">
-        <v>4.662682771682739</v>
+        <v>5.367540836334229</v>
       </c>
       <c r="G16" t="n">
-        <v>4.396134376525879</v>
+        <v>5.188739061355591</v>
       </c>
       <c r="H16" t="n">
-        <v>4.995366334915161</v>
+        <v>5.120857000350952</v>
       </c>
       <c r="I16" t="n">
-        <v>4.796643733978271</v>
+        <v>4.921887636184692</v>
       </c>
       <c r="J16" t="n">
-        <v>4.423737525939941</v>
+        <v>4.958162546157837</v>
       </c>
       <c r="K16" t="n">
-        <v>4.654094219207764</v>
+        <v>4.332657098770142</v>
       </c>
       <c r="L16" t="n">
-        <v>4.661244964599609</v>
+        <v>4.918125414848328</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>4.754074811935425</v>
+        <v>4.608675003051758</v>
       </c>
       <c r="C17" t="n">
-        <v>5.03298282623291</v>
+        <v>4.790387630462646</v>
       </c>
       <c r="D17" t="n">
-        <v>5.840411424636841</v>
+        <v>5.270904302597046</v>
       </c>
       <c r="E17" t="n">
-        <v>5.357852697372437</v>
+        <v>4.830082654953003</v>
       </c>
       <c r="F17" t="n">
-        <v>4.778831243515015</v>
+        <v>4.711401462554932</v>
       </c>
       <c r="G17" t="n">
-        <v>5.04697322845459</v>
+        <v>4.841053485870361</v>
       </c>
       <c r="H17" t="n">
-        <v>5.278920412063599</v>
+        <v>4.716687440872192</v>
       </c>
       <c r="I17" t="n">
-        <v>5.366512775421143</v>
+        <v>4.931847095489502</v>
       </c>
       <c r="J17" t="n">
-        <v>4.939666032791138</v>
+        <v>4.397241115570068</v>
       </c>
       <c r="K17" t="n">
-        <v>4.858211994171143</v>
+        <v>4.713789939880371</v>
       </c>
       <c r="L17" t="n">
-        <v>5.125443744659424</v>
+        <v>4.781207013130188</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>4.838325262069702</v>
+        <v>5.701752662658691</v>
       </c>
       <c r="C18" t="n">
-        <v>5.395543813705444</v>
+        <v>5.933634996414185</v>
       </c>
       <c r="D18" t="n">
-        <v>5.252034664154053</v>
+        <v>5.269906282424927</v>
       </c>
       <c r="E18" t="n">
-        <v>4.82547402381897</v>
+        <v>4.281550645828247</v>
       </c>
       <c r="F18" t="n">
-        <v>5.473965406417847</v>
+        <v>4.798168897628784</v>
       </c>
       <c r="G18" t="n">
-        <v>4.865441083908081</v>
+        <v>4.523823261260986</v>
       </c>
       <c r="H18" t="n">
-        <v>5.050020217895508</v>
+        <v>4.670510053634644</v>
       </c>
       <c r="I18" t="n">
-        <v>4.712908029556274</v>
+        <v>4.810137271881104</v>
       </c>
       <c r="J18" t="n">
-        <v>4.790129423141479</v>
+        <v>4.621640920639038</v>
       </c>
       <c r="K18" t="n">
-        <v>5.05933690071106</v>
+        <v>4.633609056472778</v>
       </c>
       <c r="L18" t="n">
-        <v>5.026317882537842</v>
+        <v>4.924473404884338</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>4.672626733779907</v>
+        <v>4.898896932601929</v>
       </c>
       <c r="C19" t="n">
-        <v>4.936957836151123</v>
+        <v>4.278558015823364</v>
       </c>
       <c r="D19" t="n">
-        <v>4.555763721466064</v>
+        <v>4.213731288909912</v>
       </c>
       <c r="E19" t="n">
-        <v>5.589598178863525</v>
+        <v>5.298240423202515</v>
       </c>
       <c r="F19" t="n">
-        <v>4.95603084564209</v>
+        <v>4.355352401733398</v>
       </c>
       <c r="G19" t="n">
-        <v>5.436146259307861</v>
+        <v>5.034834861755371</v>
       </c>
       <c r="H19" t="n">
-        <v>4.892996072769165</v>
+        <v>4.057151079177856</v>
       </c>
       <c r="I19" t="n">
-        <v>4.979704856872559</v>
+        <v>4.011272430419922</v>
       </c>
       <c r="J19" t="n">
-        <v>5.236579418182373</v>
+        <v>4.354355812072754</v>
       </c>
       <c r="K19" t="n">
-        <v>5.317017078399658</v>
+        <v>5.116317272186279</v>
       </c>
       <c r="L19" t="n">
-        <v>5.057342100143432</v>
+        <v>4.56187105178833</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>5.522487163543701</v>
+        <v>4.930813550949097</v>
       </c>
       <c r="C20" t="n">
-        <v>5.586593866348267</v>
+        <v>4.961028099060059</v>
       </c>
       <c r="D20" t="n">
-        <v>5.310308218002319</v>
+        <v>4.85900616645813</v>
       </c>
       <c r="E20" t="n">
-        <v>5.670210599899292</v>
+        <v>4.7403244972229</v>
       </c>
       <c r="F20" t="n">
-        <v>4.800934076309204</v>
+        <v>4.808141946792603</v>
       </c>
       <c r="G20" t="n">
-        <v>5.316314697265625</v>
+        <v>5.433313131332397</v>
       </c>
       <c r="H20" t="n">
-        <v>5.38471531867981</v>
+        <v>5.498296737670898</v>
       </c>
       <c r="I20" t="n">
-        <v>5.512990236282349</v>
+        <v>4.502964973449707</v>
       </c>
       <c r="J20" t="n">
-        <v>5.626090049743652</v>
+        <v>5.771565437316895</v>
       </c>
       <c r="K20" t="n">
-        <v>6.224863529205322</v>
+        <v>4.612665176391602</v>
       </c>
       <c r="L20" t="n">
-        <v>5.495550775527954</v>
+        <v>5.011811971664429</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>5.720083713531494</v>
+        <v>5.364653825759888</v>
       </c>
       <c r="C21" t="n">
-        <v>4.75492525100708</v>
+        <v>4.886931180953979</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022409677505493</v>
+        <v>4.045182228088379</v>
       </c>
       <c r="E21" t="n">
-        <v>5.256192207336426</v>
+        <v>4.289528369903564</v>
       </c>
       <c r="F21" t="n">
-        <v>6.356442213058472</v>
+        <v>4.204756259918213</v>
       </c>
       <c r="G21" t="n">
-        <v>4.579437971115112</v>
+        <v>4.36732006072998</v>
       </c>
       <c r="H21" t="n">
-        <v>5.551522493362427</v>
+        <v>4.485006332397461</v>
       </c>
       <c r="I21" t="n">
-        <v>5.299130201339722</v>
+        <v>4.984669923782349</v>
       </c>
       <c r="J21" t="n">
-        <v>5.254522085189819</v>
+        <v>4.586734056472778</v>
       </c>
       <c r="K21" t="n">
-        <v>4.835294008255005</v>
+        <v>4.346624135971069</v>
       </c>
       <c r="L21" t="n">
-        <v>5.262995982170105</v>
+        <v>4.556140637397766</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>5.840142250061035</v>
+        <v>5.102355241775513</v>
       </c>
       <c r="C22" t="n">
-        <v>5.588561296463013</v>
+        <v>4.372327327728271</v>
       </c>
       <c r="D22" t="n">
-        <v>5.430496215820312</v>
+        <v>4.745309829711914</v>
       </c>
       <c r="E22" t="n">
-        <v>5.741106271743774</v>
+        <v>5.152220964431763</v>
       </c>
       <c r="F22" t="n">
-        <v>5.219156742095947</v>
+        <v>4.749299287796021</v>
       </c>
       <c r="G22" t="n">
-        <v>5.77663516998291</v>
+        <v>5.172168731689453</v>
       </c>
       <c r="H22" t="n">
-        <v>4.794053554534912</v>
+        <v>4.611667156219482</v>
       </c>
       <c r="I22" t="n">
-        <v>5.352460622787476</v>
+        <v>4.590723276138306</v>
       </c>
       <c r="J22" t="n">
-        <v>4.729068517684937</v>
+        <v>4.943779230117798</v>
       </c>
       <c r="K22" t="n">
-        <v>4.944643020629883</v>
+        <v>5.586060762405396</v>
       </c>
       <c r="L22" t="n">
-        <v>5.34163236618042</v>
+        <v>4.902591180801392</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>5.251009464263916</v>
+        <v>5.309799909591675</v>
       </c>
       <c r="C23" t="n">
-        <v>4.992001295089722</v>
+        <v>4.983516931533813</v>
       </c>
       <c r="D23" t="n">
-        <v>4.44351863861084</v>
+        <v>4.333411693572998</v>
       </c>
       <c r="E23" t="n">
-        <v>5.314409017562866</v>
+        <v>4.841200113296509</v>
       </c>
       <c r="F23" t="n">
-        <v>4.994575262069702</v>
+        <v>4.158772945404053</v>
       </c>
       <c r="G23" t="n">
-        <v>5.581499576568604</v>
+        <v>4.573768854141235</v>
       </c>
       <c r="H23" t="n">
-        <v>5.081722259521484</v>
+        <v>4.378291368484497</v>
       </c>
       <c r="I23" t="n">
-        <v>5.572901248931885</v>
+        <v>4.007186412811279</v>
       </c>
       <c r="J23" t="n">
-        <v>5.430505275726318</v>
+        <v>4.354355335235596</v>
       </c>
       <c r="K23" t="n">
-        <v>5.06927227973938</v>
+        <v>4.268584728240967</v>
       </c>
       <c r="L23" t="n">
-        <v>5.173141431808472</v>
+        <v>4.520888829231263</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>5.496578216552734</v>
+        <v>4.464062213897705</v>
       </c>
       <c r="C24" t="n">
-        <v>5.175572395324707</v>
+        <v>4.286535739898682</v>
       </c>
       <c r="D24" t="n">
-        <v>4.809909105300903</v>
+        <v>4.467401027679443</v>
       </c>
       <c r="E24" t="n">
-        <v>4.844368696212769</v>
+        <v>5.066451072692871</v>
       </c>
       <c r="F24" t="n">
-        <v>5.452278137207031</v>
+        <v>4.307481527328491</v>
       </c>
       <c r="G24" t="n">
-        <v>4.971423149108887</v>
+        <v>4.598702669143677</v>
       </c>
       <c r="H24" t="n">
-        <v>5.097461462020874</v>
+        <v>4.373693227767944</v>
       </c>
       <c r="I24" t="n">
-        <v>5.257989645004272</v>
+        <v>4.409308910369873</v>
       </c>
       <c r="J24" t="n">
-        <v>4.855531692504883</v>
+        <v>4.47164511680603</v>
       </c>
       <c r="K24" t="n">
-        <v>5.140880584716797</v>
+        <v>4.374413728713989</v>
       </c>
       <c r="L24" t="n">
-        <v>5.110199308395385</v>
+        <v>4.48196952342987</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>4.986660003662109</v>
+        <v>4.201367139816284</v>
       </c>
       <c r="C25" t="n">
-        <v>4.64057183265686</v>
+        <v>3.97561502456665</v>
       </c>
       <c r="D25" t="n">
-        <v>4.52753758430481</v>
+        <v>4.776912927627563</v>
       </c>
       <c r="E25" t="n">
-        <v>4.612306594848633</v>
+        <v>4.267587184906006</v>
       </c>
       <c r="F25" t="n">
-        <v>5.163422584533691</v>
+        <v>4.340392827987671</v>
       </c>
       <c r="G25" t="n">
-        <v>4.639329195022583</v>
+        <v>5.565117359161377</v>
       </c>
       <c r="H25" t="n">
-        <v>5.432648897171021</v>
+        <v>4.050169467926025</v>
       </c>
       <c r="I25" t="n">
-        <v>4.071435928344727</v>
+        <v>4.949762582778931</v>
       </c>
       <c r="J25" t="n">
-        <v>4.800986766815186</v>
+        <v>4.981678009033203</v>
       </c>
       <c r="K25" t="n">
-        <v>4.836997270584106</v>
+        <v>4.45009970664978</v>
       </c>
       <c r="L25" t="n">
-        <v>4.771189665794372</v>
+        <v>4.555870223045349</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>5.528465032577515</v>
+        <v>4.959736585617065</v>
       </c>
       <c r="C26" t="n">
-        <v>5.053229093551636</v>
+        <v>5.451421022415161</v>
       </c>
       <c r="D26" t="n">
-        <v>5.311717748641968</v>
+        <v>4.818115234375</v>
       </c>
       <c r="E26" t="n">
-        <v>4.965927124023438</v>
+        <v>4.90986967086792</v>
       </c>
       <c r="F26" t="n">
-        <v>5.090271711349487</v>
+        <v>5.41746997833252</v>
       </c>
       <c r="G26" t="n">
-        <v>5.315114259719849</v>
+        <v>4.984669923782349</v>
       </c>
       <c r="H26" t="n">
-        <v>4.798436164855957</v>
+        <v>4.705416679382324</v>
       </c>
       <c r="I26" t="n">
-        <v>5.080139875411987</v>
+        <v>4.891905069351196</v>
       </c>
       <c r="J26" t="n">
-        <v>4.949016809463501</v>
+        <v>4.841055154800415</v>
       </c>
       <c r="K26" t="n">
-        <v>5.859838485717773</v>
+        <v>4.88094687461853</v>
       </c>
       <c r="L26" t="n">
-        <v>5.195215630531311</v>
+        <v>4.986060619354248</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>4.922351837158203</v>
+        <v>5.247966051101685</v>
       </c>
       <c r="C27" t="n">
-        <v>4.444411993026733</v>
+        <v>4.480020046234131</v>
       </c>
       <c r="D27" t="n">
-        <v>4.171727418899536</v>
+        <v>4.22470235824585</v>
       </c>
       <c r="E27" t="n">
-        <v>4.249825477600098</v>
+        <v>4.359310865402222</v>
       </c>
       <c r="F27" t="n">
-        <v>4.529572248458862</v>
+        <v>4.686467885971069</v>
       </c>
       <c r="G27" t="n">
-        <v>4.501899242401123</v>
+        <v>4.418383836746216</v>
       </c>
       <c r="H27" t="n">
-        <v>5.077060222625732</v>
+        <v>4.059742450714111</v>
       </c>
       <c r="I27" t="n">
-        <v>4.068583488464355</v>
+        <v>4.451096773147583</v>
       </c>
       <c r="J27" t="n">
-        <v>5.561344623565674</v>
+        <v>5.623959302902222</v>
       </c>
       <c r="K27" t="n">
-        <v>5.709054946899414</v>
+        <v>4.217060565948486</v>
       </c>
       <c r="L27" t="n">
-        <v>4.723583149909973</v>
+        <v>4.576871013641357</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>5.01704740524292</v>
+        <v>3.890080690383911</v>
       </c>
       <c r="C28" t="n">
-        <v>4.227420568466187</v>
+        <v>4.1858069896698</v>
       </c>
       <c r="D28" t="n">
-        <v>5.306424617767334</v>
+        <v>4.859005928039551</v>
       </c>
       <c r="E28" t="n">
-        <v>4.184362411499023</v>
+        <v>4.018254041671753</v>
       </c>
       <c r="F28" t="n">
-        <v>4.61292576789856</v>
+        <v>4.427161455154419</v>
       </c>
       <c r="G28" t="n">
-        <v>4.325149774551392</v>
+        <v>4.117987871170044</v>
       </c>
       <c r="H28" t="n">
-        <v>5.537137508392334</v>
+        <v>3.910542964935303</v>
       </c>
       <c r="I28" t="n">
-        <v>4.904778718948364</v>
+        <v>3.778894424438477</v>
       </c>
       <c r="J28" t="n">
-        <v>4.451937437057495</v>
+        <v>4.020249605178833</v>
       </c>
       <c r="K28" t="n">
-        <v>4.769651174545288</v>
+        <v>4.007283449172974</v>
       </c>
       <c r="L28" t="n">
-        <v>4.73368353843689</v>
+        <v>4.121526741981507</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>4.394431829452515</v>
+        <v>4.474035739898682</v>
       </c>
       <c r="C29" t="n">
-        <v>5.429448127746582</v>
+        <v>4.720974206924438</v>
       </c>
       <c r="D29" t="n">
-        <v>4.338043451309204</v>
+        <v>5.023566246032715</v>
       </c>
       <c r="E29" t="n">
-        <v>3.931549310684204</v>
+        <v>4.51293158531189</v>
       </c>
       <c r="F29" t="n">
-        <v>4.223896980285645</v>
+        <v>4.479987859725952</v>
       </c>
       <c r="G29" t="n">
-        <v>4.504230260848999</v>
+        <v>5.760595798492432</v>
       </c>
       <c r="H29" t="n">
-        <v>4.191574096679688</v>
+        <v>4.283337831497192</v>
       </c>
       <c r="I29" t="n">
-        <v>4.360705614089966</v>
+        <v>5.237869024276733</v>
       </c>
       <c r="J29" t="n">
-        <v>4.390040159225464</v>
+        <v>5.077460050582886</v>
       </c>
       <c r="K29" t="n">
-        <v>3.995324373245239</v>
+        <v>5.463255882263184</v>
       </c>
       <c r="L29" t="n">
-        <v>4.375924420356751</v>
+        <v>4.90340142250061</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>4.716334104537964</v>
+        <v>4.54314112663269</v>
       </c>
       <c r="C30" t="n">
-        <v>4.525713205337524</v>
+        <v>4.942818403244019</v>
       </c>
       <c r="D30" t="n">
-        <v>4.832904100418091</v>
+        <v>4.125273942947388</v>
       </c>
       <c r="E30" t="n">
-        <v>5.140140771865845</v>
+        <v>5.42948055267334</v>
       </c>
       <c r="F30" t="n">
-        <v>5.00974178314209</v>
+        <v>4.155035018920898</v>
       </c>
       <c r="G30" t="n">
-        <v>4.484161376953125</v>
+        <v>4.855051040649414</v>
       </c>
       <c r="H30" t="n">
-        <v>4.329931020736694</v>
+        <v>4.689458847045898</v>
       </c>
       <c r="I30" t="n">
-        <v>4.445196628570557</v>
+        <v>3.874638319015503</v>
       </c>
       <c r="J30" t="n">
-        <v>4.668414354324341</v>
+        <v>4.465349435806274</v>
       </c>
       <c r="K30" t="n">
-        <v>5.152601718902588</v>
+        <v>6.11458945274353</v>
       </c>
       <c r="L30" t="n">
-        <v>4.730513906478881</v>
+        <v>4.719483613967896</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>5.627016067504883</v>
+        <v>4.758275270462036</v>
       </c>
       <c r="C31" t="n">
-        <v>5.629486799240112</v>
+        <v>5.175160884857178</v>
       </c>
       <c r="D31" t="n">
-        <v>5.740080595016479</v>
+        <v>5.167182445526123</v>
       </c>
       <c r="E31" t="n">
-        <v>5.103658437728882</v>
+        <v>5.043665409088135</v>
       </c>
       <c r="F31" t="n">
-        <v>5.420387029647827</v>
+        <v>5.610529899597168</v>
       </c>
       <c r="G31" t="n">
-        <v>5.8963623046875</v>
+        <v>5.511278867721558</v>
       </c>
       <c r="H31" t="n">
-        <v>5.41100811958313</v>
+        <v>5.432507038116455</v>
       </c>
       <c r="I31" t="n">
-        <v>5.516230583190918</v>
+        <v>4.996637582778931</v>
       </c>
       <c r="J31" t="n">
-        <v>5.392101526260376</v>
+        <v>4.622239589691162</v>
       </c>
       <c r="K31" t="n">
-        <v>5.50348424911499</v>
+        <v>4.903923749923706</v>
       </c>
       <c r="L31" t="n">
-        <v>5.52398157119751</v>
+        <v>5.122140073776245</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>5.843198299407959</v>
+        <v>5.466121912002563</v>
       </c>
       <c r="C32" t="n">
-        <v>5.287810087203979</v>
+        <v>5.671794652938843</v>
       </c>
       <c r="D32" t="n">
-        <v>4.778107404708862</v>
+        <v>6.274256706237793</v>
       </c>
       <c r="E32" t="n">
-        <v>4.778559446334839</v>
+        <v>5.288638353347778</v>
       </c>
       <c r="F32" t="n">
-        <v>4.584492206573486</v>
+        <v>5.418509721755981</v>
       </c>
       <c r="G32" t="n">
-        <v>4.974417924880981</v>
+        <v>5.181144952774048</v>
       </c>
       <c r="H32" t="n">
-        <v>4.714040040969849</v>
+        <v>4.916586875915527</v>
       </c>
       <c r="I32" t="n">
-        <v>5.093889951705933</v>
+        <v>5.107341766357422</v>
       </c>
       <c r="J32" t="n">
-        <v>4.606868267059326</v>
+        <v>4.99374532699585</v>
       </c>
       <c r="K32" t="n">
-        <v>5.062128305435181</v>
+        <v>5.266947269439697</v>
       </c>
       <c r="L32" t="n">
-        <v>4.97235119342804</v>
+        <v>5.35850875377655</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>4.452787399291992</v>
+        <v>6.104688167572021</v>
       </c>
       <c r="C33" t="n">
-        <v>5.021775007247925</v>
+        <v>5.8563392162323</v>
       </c>
       <c r="D33" t="n">
-        <v>5.37559700012207</v>
+        <v>4.593716144561768</v>
       </c>
       <c r="E33" t="n">
-        <v>4.736864805221558</v>
+        <v>4.203223466873169</v>
       </c>
       <c r="F33" t="n">
-        <v>5.231320142745972</v>
+        <v>4.711865425109863</v>
       </c>
       <c r="G33" t="n">
-        <v>5.182329416275024</v>
+        <v>5.620126008987427</v>
       </c>
       <c r="H33" t="n">
-        <v>4.851405143737793</v>
+        <v>5.247897148132324</v>
       </c>
       <c r="I33" t="n">
-        <v>5.43921947479248</v>
+        <v>4.502430200576782</v>
       </c>
       <c r="J33" t="n">
-        <v>5.978776693344116</v>
+        <v>4.505950689315796</v>
       </c>
       <c r="K33" t="n">
-        <v>5.011454582214355</v>
+        <v>5.534200668334961</v>
       </c>
       <c r="L33" t="n">
-        <v>5.128152966499329</v>
+        <v>5.088043713569641</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>4.641710996627808</v>
+        <v>3.913227319717407</v>
       </c>
       <c r="C34" t="n">
-        <v>4.372613430023193</v>
+        <v>4.867026805877686</v>
       </c>
       <c r="D34" t="n">
-        <v>5.247850179672241</v>
+        <v>4.741395950317383</v>
       </c>
       <c r="E34" t="n">
-        <v>4.107248067855835</v>
+        <v>5.126674652099609</v>
       </c>
       <c r="F34" t="n">
-        <v>4.03555965423584</v>
+        <v>4.2609543800354</v>
       </c>
       <c r="G34" t="n">
-        <v>5.224716901779175</v>
+        <v>4.994679927825928</v>
       </c>
       <c r="H34" t="n">
-        <v>4.048675537109375</v>
+        <v>4.300679445266724</v>
       </c>
       <c r="I34" t="n">
-        <v>4.198596000671387</v>
+        <v>4.733402729034424</v>
       </c>
       <c r="J34" t="n">
-        <v>4.694047927856445</v>
+        <v>3.8267662525177</v>
       </c>
       <c r="K34" t="n">
-        <v>4.495490074157715</v>
+        <v>5.048847436904907</v>
       </c>
       <c r="L34" t="n">
-        <v>4.506650876998902</v>
+        <v>4.581365489959717</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>5.321550369262695</v>
+        <v>5.182141065597534</v>
       </c>
       <c r="C35" t="n">
-        <v>3.946832418441772</v>
+        <v>4.032217264175415</v>
       </c>
       <c r="D35" t="n">
-        <v>4.591614246368408</v>
+        <v>4.875953197479248</v>
       </c>
       <c r="E35" t="n">
-        <v>3.995576620101929</v>
+        <v>4.154890775680542</v>
       </c>
       <c r="F35" t="n">
-        <v>5.110275745391846</v>
+        <v>4.970619440078735</v>
       </c>
       <c r="G35" t="n">
-        <v>4.140081882476807</v>
+        <v>4.40329384803772</v>
       </c>
       <c r="H35" t="n">
-        <v>3.943987607955933</v>
+        <v>3.917838573455811</v>
       </c>
       <c r="I35" t="n">
-        <v>4.271885633468628</v>
+        <v>3.813280820846558</v>
       </c>
       <c r="J35" t="n">
-        <v>4.406427145004272</v>
+        <v>4.468147754669189</v>
       </c>
       <c r="K35" t="n">
-        <v>4.026607990264893</v>
+        <v>3.857482433319092</v>
       </c>
       <c r="L35" t="n">
-        <v>4.375483965873718</v>
+        <v>4.367586517333985</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>5.324769973754883</v>
+        <v>5.104349613189697</v>
       </c>
       <c r="C36" t="n">
-        <v>4.547306537628174</v>
+        <v>4.931811809539795</v>
       </c>
       <c r="D36" t="n">
-        <v>4.80656099319458</v>
+        <v>4.542181253433228</v>
       </c>
       <c r="E36" t="n">
-        <v>4.508867025375366</v>
+        <v>4.971015453338623</v>
       </c>
       <c r="F36" t="n">
-        <v>4.608078241348267</v>
+        <v>4.465093851089478</v>
       </c>
       <c r="G36" t="n">
-        <v>4.331977844238281</v>
+        <v>5.052946090698242</v>
       </c>
       <c r="H36" t="n">
-        <v>4.955699682235718</v>
+        <v>5.226024627685547</v>
       </c>
       <c r="I36" t="n">
-        <v>5.196799039840698</v>
+        <v>5.101259708404541</v>
       </c>
       <c r="J36" t="n">
-        <v>5.271904706954956</v>
+        <v>5.816930770874023</v>
       </c>
       <c r="K36" t="n">
-        <v>5.537496328353882</v>
+        <v>5.904607057571411</v>
       </c>
       <c r="L36" t="n">
-        <v>4.90894603729248</v>
+        <v>5.111622023582458</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>5.148432493209839</v>
+        <v>7.461379289627075</v>
       </c>
       <c r="C37" t="n">
-        <v>5.915681600570679</v>
+        <v>6.250342130661011</v>
       </c>
       <c r="D37" t="n">
-        <v>5.539323806762695</v>
+        <v>5.000039339065552</v>
       </c>
       <c r="E37" t="n">
-        <v>5.907150030136108</v>
+        <v>5.121585607528687</v>
       </c>
       <c r="F37" t="n">
-        <v>5.485690116882324</v>
+        <v>5.977062702178955</v>
       </c>
       <c r="G37" t="n">
-        <v>5.866962194442749</v>
+        <v>5.604349613189697</v>
       </c>
       <c r="H37" t="n">
-        <v>5.784275770187378</v>
+        <v>5.907249212265015</v>
       </c>
       <c r="I37" t="n">
-        <v>5.32007908821106</v>
+        <v>5.844369888305664</v>
       </c>
       <c r="J37" t="n">
-        <v>5.626378774642944</v>
+        <v>6.373955965042114</v>
       </c>
       <c r="K37" t="n">
-        <v>5.150440216064453</v>
+        <v>5.286471605300903</v>
       </c>
       <c r="L37" t="n">
-        <v>5.574441409111023</v>
+        <v>5.882680535316467</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>4.216066122055054</v>
+        <v>4.929494619369507</v>
       </c>
       <c r="C38" t="n">
-        <v>4.28402304649353</v>
+        <v>5.215772390365601</v>
       </c>
       <c r="D38" t="n">
-        <v>5.125058650970459</v>
+        <v>4.437184810638428</v>
       </c>
       <c r="E38" t="n">
-        <v>4.165705919265747</v>
+        <v>5.207083463668823</v>
       </c>
       <c r="F38" t="n">
-        <v>4.7564537525177</v>
+        <v>4.738367080688477</v>
       </c>
       <c r="G38" t="n">
-        <v>4.348816156387329</v>
+        <v>4.551042556762695</v>
       </c>
       <c r="H38" t="n">
-        <v>4.311264753341675</v>
+        <v>4.6439049243927</v>
       </c>
       <c r="I38" t="n">
-        <v>4.578870534896851</v>
+        <v>5.85668158531189</v>
       </c>
       <c r="J38" t="n">
-        <v>4.251515626907349</v>
+        <v>4.386318683624268</v>
       </c>
       <c r="K38" t="n">
-        <v>5.088726997375488</v>
+        <v>4.671627283096313</v>
       </c>
       <c r="L38" t="n">
-        <v>4.512650156021119</v>
+        <v>4.86374773979187</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>4.676051378250122</v>
+        <v>4.151249408721924</v>
       </c>
       <c r="C39" t="n">
-        <v>4.199511289596558</v>
+        <v>4.696241140365601</v>
       </c>
       <c r="D39" t="n">
-        <v>4.277531623840332</v>
+        <v>4.866827011108398</v>
       </c>
       <c r="E39" t="n">
-        <v>4.175536155700684</v>
+        <v>5.725078821182251</v>
       </c>
       <c r="F39" t="n">
-        <v>3.910723686218262</v>
+        <v>6.233304023742676</v>
       </c>
       <c r="G39" t="n">
-        <v>4.875570058822632</v>
+        <v>5.639775276184082</v>
       </c>
       <c r="H39" t="n">
-        <v>4.052966117858887</v>
+        <v>4.407624483108521</v>
       </c>
       <c r="I39" t="n">
-        <v>4.320232152938843</v>
+        <v>5.206076622009277</v>
       </c>
       <c r="J39" t="n">
-        <v>4.730937242507935</v>
+        <v>6.449314117431641</v>
       </c>
       <c r="K39" t="n">
-        <v>4.430215835571289</v>
+        <v>8.444691896438599</v>
       </c>
       <c r="L39" t="n">
-        <v>4.364927554130555</v>
+        <v>5.582018280029297</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>5.513917207717896</v>
+        <v>6.303144454956055</v>
       </c>
       <c r="C40" t="n">
-        <v>5.279561996459961</v>
+        <v>6.606416940689087</v>
       </c>
       <c r="D40" t="n">
-        <v>5.495450973510742</v>
+        <v>5.717435359954834</v>
       </c>
       <c r="E40" t="n">
-        <v>5.352547645568848</v>
+        <v>5.534059762954712</v>
       </c>
       <c r="F40" t="n">
-        <v>5.028182983398438</v>
+        <v>7.093110084533691</v>
       </c>
       <c r="G40" t="n">
-        <v>4.898838520050049</v>
+        <v>8.783503770828247</v>
       </c>
       <c r="H40" t="n">
-        <v>4.717784643173218</v>
+        <v>9.197548389434814</v>
       </c>
       <c r="I40" t="n">
-        <v>5.529944896697998</v>
+        <v>7.197541952133179</v>
       </c>
       <c r="J40" t="n">
-        <v>5.79174280166626</v>
+        <v>6.617263555526733</v>
       </c>
       <c r="K40" t="n">
-        <v>4.748210668563843</v>
+        <v>5.746336698532104</v>
       </c>
       <c r="L40" t="n">
-        <v>5.235618233680725</v>
+        <v>6.879636096954346</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>4.272783279418945</v>
+        <v>5.600552797317505</v>
       </c>
       <c r="C41" t="n">
-        <v>4.349316358566284</v>
+        <v>6.268188238143921</v>
       </c>
       <c r="D41" t="n">
-        <v>5.059354543685913</v>
+        <v>4.426517486572266</v>
       </c>
       <c r="E41" t="n">
-        <v>4.594627618789673</v>
+        <v>4.740580797195435</v>
       </c>
       <c r="F41" t="n">
-        <v>4.571815729141235</v>
+        <v>5.317360877990723</v>
       </c>
       <c r="G41" t="n">
-        <v>4.810100793838501</v>
+        <v>4.305812120437622</v>
       </c>
       <c r="H41" t="n">
-        <v>4.502890110015869</v>
+        <v>4.950622081756592</v>
       </c>
       <c r="I41" t="n">
-        <v>4.55397629737854</v>
+        <v>5.243976831436157</v>
       </c>
       <c r="J41" t="n">
-        <v>5.254230499267578</v>
+        <v>5.444439888000488</v>
       </c>
       <c r="K41" t="n">
-        <v>5.245553255081177</v>
+        <v>4.910858869552612</v>
       </c>
       <c r="L41" t="n">
-        <v>4.721464848518371</v>
+        <v>5.120890998840332</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>6.177718877792358</v>
+        <v>7.210717916488647</v>
       </c>
       <c r="C42" t="n">
-        <v>5.287732601165771</v>
+        <v>7.775207281112671</v>
       </c>
       <c r="D42" t="n">
-        <v>5.241025686264038</v>
+        <v>6.133597850799561</v>
       </c>
       <c r="E42" t="n">
-        <v>4.933624982833862</v>
+        <v>5.426488161087036</v>
       </c>
       <c r="F42" t="n">
-        <v>5.138559579849243</v>
+        <v>6.704370260238647</v>
       </c>
       <c r="G42" t="n">
-        <v>5.290482521057129</v>
+        <v>5.361662626266479</v>
       </c>
       <c r="H42" t="n">
-        <v>4.840072870254517</v>
+        <v>5.370348930358887</v>
       </c>
       <c r="I42" t="n">
-        <v>4.932059049606323</v>
+        <v>5.694771528244019</v>
       </c>
       <c r="J42" t="n">
-        <v>5.045944213867188</v>
+        <v>8.083012342453003</v>
       </c>
       <c r="K42" t="n">
-        <v>5.378524541854858</v>
+        <v>6.97977876663208</v>
       </c>
       <c r="L42" t="n">
-        <v>5.226574492454529</v>
+        <v>6.473995566368103</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>5.547130346298218</v>
+        <v>5.721699714660645</v>
       </c>
       <c r="C43" t="n">
-        <v>5.150322437286377</v>
+        <v>5.549573183059692</v>
       </c>
       <c r="D43" t="n">
-        <v>5.17588996887207</v>
+        <v>7.478656053543091</v>
       </c>
       <c r="E43" t="n">
-        <v>4.998500823974609</v>
+        <v>7.730165958404541</v>
       </c>
       <c r="F43" t="n">
-        <v>4.708785057067871</v>
+        <v>7.321018218994141</v>
       </c>
       <c r="G43" t="n">
-        <v>5.576177358627319</v>
+        <v>7.845908403396606</v>
       </c>
       <c r="H43" t="n">
-        <v>5.073601245880127</v>
+        <v>4.755283355712891</v>
       </c>
       <c r="I43" t="n">
-        <v>4.802033185958862</v>
+        <v>5.774558305740356</v>
       </c>
       <c r="J43" t="n">
-        <v>4.695389032363892</v>
+        <v>5.693549871444702</v>
       </c>
       <c r="K43" t="n">
-        <v>5.005414962768555</v>
+        <v>5.562180519104004</v>
       </c>
       <c r="L43" t="n">
-        <v>5.07332444190979</v>
+        <v>6.343259358406067</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>5.07349705696106</v>
+        <v>5.836491823196411</v>
       </c>
       <c r="C44" t="n">
-        <v>5.053762435913086</v>
+        <v>5.559316635131836</v>
       </c>
       <c r="D44" t="n">
-        <v>4.881120681762695</v>
+        <v>4.352360248565674</v>
       </c>
       <c r="E44" t="n">
-        <v>4.897645711898804</v>
+        <v>4.789787292480469</v>
       </c>
       <c r="F44" t="n">
-        <v>4.507118940353394</v>
+        <v>5.024184703826904</v>
       </c>
       <c r="G44" t="n">
-        <v>4.665276765823364</v>
+        <v>4.732401609420776</v>
       </c>
       <c r="H44" t="n">
-        <v>5.018920183181763</v>
+        <v>4.966718196868896</v>
       </c>
       <c r="I44" t="n">
-        <v>4.680714130401611</v>
+        <v>4.465059995651245</v>
       </c>
       <c r="J44" t="n">
-        <v>5.09989857673645</v>
+        <v>4.523900985717773</v>
       </c>
       <c r="K44" t="n">
-        <v>4.634445905685425</v>
+        <v>4.406216859817505</v>
       </c>
       <c r="L44" t="n">
-        <v>4.851240038871765</v>
+        <v>4.865643835067749</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>4.920130014419556</v>
+        <v>4.226555109024048</v>
       </c>
       <c r="C45" t="n">
-        <v>4.452991724014282</v>
+        <v>5.72303032875061</v>
       </c>
       <c r="D45" t="n">
-        <v>4.584805011749268</v>
+        <v>4.174569845199585</v>
       </c>
       <c r="E45" t="n">
-        <v>4.270305633544922</v>
+        <v>4.387300729751587</v>
       </c>
       <c r="F45" t="n">
-        <v>4.563295841217041</v>
+        <v>4.365325689315796</v>
       </c>
       <c r="G45" t="n">
-        <v>5.259783506393433</v>
+        <v>5.268599987030029</v>
       </c>
       <c r="H45" t="n">
-        <v>5.315579175949097</v>
+        <v>4.354230165481567</v>
       </c>
       <c r="I45" t="n">
-        <v>6.915430068969727</v>
+        <v>3.947811841964722</v>
       </c>
       <c r="J45" t="n">
-        <v>4.702516794204712</v>
+        <v>5.426542520523071</v>
       </c>
       <c r="K45" t="n">
-        <v>5.426674365997314</v>
+        <v>4.399733066558838</v>
       </c>
       <c r="L45" t="n">
-        <v>5.041151213645935</v>
+        <v>4.627369928359985</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>5.946600675582886</v>
+        <v>4.801198720932007</v>
       </c>
       <c r="C46" t="n">
-        <v>5.84827184677124</v>
+        <v>4.536912202835083</v>
       </c>
       <c r="D46" t="n">
-        <v>5.354738712310791</v>
+        <v>4.303491115570068</v>
       </c>
       <c r="E46" t="n">
-        <v>6.652895927429199</v>
+        <v>5.517245769500732</v>
       </c>
       <c r="F46" t="n">
-        <v>4.472039222717285</v>
+        <v>4.472182989120483</v>
       </c>
       <c r="G46" t="n">
-        <v>5.334002256393433</v>
+        <v>4.606256723403931</v>
       </c>
       <c r="H46" t="n">
-        <v>4.846983909606934</v>
+        <v>4.579832077026367</v>
       </c>
       <c r="I46" t="n">
-        <v>5.690764904022217</v>
+        <v>4.581782579421997</v>
       </c>
       <c r="J46" t="n">
-        <v>4.561051607131958</v>
+        <v>4.656529664993286</v>
       </c>
       <c r="K46" t="n">
-        <v>5.319205284118652</v>
+        <v>4.465059995651245</v>
       </c>
       <c r="L46" t="n">
-        <v>5.40265543460846</v>
+        <v>4.65204918384552</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>4.135599136352539</v>
+        <v>4.803330183029175</v>
       </c>
       <c r="C47" t="n">
-        <v>3.900521278381348</v>
+        <v>5.258966684341431</v>
       </c>
       <c r="D47" t="n">
-        <v>4.615694761276245</v>
+        <v>3.782289028167725</v>
       </c>
       <c r="E47" t="n">
-        <v>4.224315166473389</v>
+        <v>4.137966632843018</v>
       </c>
       <c r="F47" t="n">
-        <v>4.885740518569946</v>
+        <v>4.719364404678345</v>
       </c>
       <c r="G47" t="n">
-        <v>5.264788627624512</v>
+        <v>4.09009575843811</v>
       </c>
       <c r="H47" t="n">
-        <v>4.251396179199219</v>
+        <v>4.104024887084961</v>
       </c>
       <c r="I47" t="n">
-        <v>4.301176309585571</v>
+        <v>4.642584562301636</v>
       </c>
       <c r="J47" t="n">
-        <v>4.534881830215454</v>
+        <v>4.393251657485962</v>
       </c>
       <c r="K47" t="n">
-        <v>4.569055795669556</v>
+        <v>4.681769132614136</v>
       </c>
       <c r="L47" t="n">
-        <v>4.468316960334778</v>
+        <v>4.46136429309845</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>4.860244274139404</v>
+        <v>5.831074714660645</v>
       </c>
       <c r="C48" t="n">
-        <v>5.435193061828613</v>
+        <v>4.720427513122559</v>
       </c>
       <c r="D48" t="n">
-        <v>5.905961513519287</v>
+        <v>4.719379186630249</v>
       </c>
       <c r="E48" t="n">
-        <v>4.852090835571289</v>
+        <v>5.026381015777588</v>
       </c>
       <c r="F48" t="n">
-        <v>4.802887201309204</v>
+        <v>5.25000786781311</v>
       </c>
       <c r="G48" t="n">
-        <v>4.676219940185547</v>
+        <v>4.83494758605957</v>
       </c>
       <c r="H48" t="n">
-        <v>5.164580106735229</v>
+        <v>5.229495525360107</v>
       </c>
       <c r="I48" t="n">
-        <v>5.267083644866943</v>
+        <v>5.209104537963867</v>
       </c>
       <c r="J48" t="n">
-        <v>5.168063879013062</v>
+        <v>5.135526657104492</v>
       </c>
       <c r="K48" t="n">
-        <v>5.0976402759552</v>
+        <v>4.904240131378174</v>
       </c>
       <c r="L48" t="n">
-        <v>5.122996473312378</v>
+        <v>5.086058473587036</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>5.046190500259399</v>
+        <v>4.856567859649658</v>
       </c>
       <c r="C49" t="n">
-        <v>5.041906833648682</v>
+        <v>4.618692874908447</v>
       </c>
       <c r="D49" t="n">
-        <v>4.928510427474976</v>
+        <v>5.450174570083618</v>
       </c>
       <c r="E49" t="n">
-        <v>4.368138551712036</v>
+        <v>4.792554140090942</v>
       </c>
       <c r="F49" t="n">
-        <v>4.612478494644165</v>
+        <v>4.509986877441406</v>
       </c>
       <c r="G49" t="n">
-        <v>4.498642683029175</v>
+        <v>5.283759117126465</v>
       </c>
       <c r="H49" t="n">
-        <v>5.325430631637573</v>
+        <v>4.769747734069824</v>
       </c>
       <c r="I49" t="n">
-        <v>4.425542593002319</v>
+        <v>4.430309772491455</v>
       </c>
       <c r="J49" t="n">
-        <v>4.517485618591309</v>
+        <v>4.699966430664062</v>
       </c>
       <c r="K49" t="n">
-        <v>4.524518013000488</v>
+        <v>5.105472803115845</v>
       </c>
       <c r="L49" t="n">
-        <v>4.728884434700012</v>
+        <v>4.851723217964173</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>4.391566038131714</v>
+        <v>3.935980081558228</v>
       </c>
       <c r="C50" t="n">
-        <v>5.21253514289856</v>
+        <v>4.328619956970215</v>
       </c>
       <c r="D50" t="n">
-        <v>4.825555324554443</v>
+        <v>4.708408832550049</v>
       </c>
       <c r="E50" t="n">
-        <v>4.732773303985596</v>
+        <v>4.889922857284546</v>
       </c>
       <c r="F50" t="n">
-        <v>4.694670915603638</v>
+        <v>4.616914033889771</v>
       </c>
       <c r="G50" t="n">
-        <v>4.961666345596313</v>
+        <v>4.52393102645874</v>
       </c>
       <c r="H50" t="n">
-        <v>4.881345272064209</v>
+        <v>4.468051195144653</v>
       </c>
       <c r="I50" t="n">
-        <v>4.133984565734863</v>
+        <v>4.596885442733765</v>
       </c>
       <c r="J50" t="n">
-        <v>4.374011993408203</v>
+        <v>4.079119205474854</v>
       </c>
       <c r="K50" t="n">
-        <v>5.116253614425659</v>
+        <v>4.52988600730896</v>
       </c>
       <c r="L50" t="n">
-        <v>4.73243625164032</v>
+        <v>4.467771863937378</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>4.833691835403442</v>
+        <v>4.658844470977783</v>
       </c>
       <c r="C51" t="n">
-        <v>4.977840423583984</v>
+        <v>4.739361524581909</v>
       </c>
       <c r="D51" t="n">
-        <v>4.801490068435669</v>
+        <v>4.657544851303101</v>
       </c>
       <c r="E51" t="n">
-        <v>4.839409351348877</v>
+        <v>4.537865161895752</v>
       </c>
       <c r="F51" t="n">
-        <v>4.549524545669556</v>
+        <v>4.41751766204834</v>
       </c>
       <c r="G51" t="n">
-        <v>4.224898815155029</v>
+        <v>4.661445617675781</v>
       </c>
       <c r="H51" t="n">
-        <v>5.765583276748657</v>
+        <v>5.252035140991211</v>
       </c>
       <c r="I51" t="n">
-        <v>4.960917711257935</v>
+        <v>4.227694034576416</v>
       </c>
       <c r="J51" t="n">
-        <v>4.623016595840454</v>
+        <v>5.163988351821899</v>
       </c>
       <c r="K51" t="n">
-        <v>4.22913646697998</v>
+        <v>5.194875717163086</v>
       </c>
       <c r="L51" t="n">
-        <v>4.780550909042359</v>
+        <v>4.751117253303528</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>5.002765121459961</v>
+        <v>5.011698350906372</v>
       </c>
       <c r="C52" t="n">
-        <v>4.861834559440613</v>
+        <v>4.953932690620422</v>
       </c>
       <c r="D52" t="n">
-        <v>4.933267378807068</v>
+        <v>4.786753749847412</v>
       </c>
       <c r="E52" t="n">
-        <v>4.907069935798645</v>
+        <v>4.910071606636047</v>
       </c>
       <c r="F52" t="n">
-        <v>4.910601677894593</v>
+        <v>4.931533403396607</v>
       </c>
       <c r="G52" t="n">
-        <v>4.961741552352906</v>
+        <v>4.990671801567077</v>
       </c>
       <c r="H52" t="n">
-        <v>4.951102352142334</v>
+        <v>4.742601804733276</v>
       </c>
       <c r="I52" t="n">
-        <v>4.926549458503723</v>
+        <v>4.813548045158386</v>
       </c>
       <c r="J52" t="n">
-        <v>4.966258172988891</v>
+        <v>4.891312370300293</v>
       </c>
       <c r="K52" t="n">
-        <v>4.96419852733612</v>
+        <v>4.95091347694397</v>
       </c>
       <c r="L52" t="n">
-        <v>4.938538873672485</v>
+        <v>4.898303730010986</v>
       </c>
     </row>
   </sheetData>
